--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5434B0B0-2ED7-6B4A-B368-E7F2DA66C0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D694A32-1E5D-F04E-A872-53BEE2388F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="200" yWindow="1380" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5080" yWindow="800" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -309,7 +309,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Mansatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
+          <t>Mandatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
         </r>
       </text>
     </comment>
@@ -318,40 +318,6 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Suruchi</author>
-  </authors>
-  <commentList>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{67DE4F7C-C44B-6949-8FCD-060A7E1D3A77}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Enter OCID of the snapshot policy to be attached to the FSS.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
@@ -596,7 +562,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Suruchi</author>
@@ -658,7 +624,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Suruchi</author>
@@ -12550,182 +12516,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
-Freeform and Defined Tags - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Enter subnet name as : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">vcn-name&gt;_&lt;subnet-name&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Source Snapshot:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accepts OCID of the source snapshot  or the name of the key defined under variable  fss_source_ocids in variables_&lt;region&gt;.tf file</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Replication Information: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Format - TargetFSS(OCID or Name)::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Defined Tags" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <u/>
@@ -12789,6 +12579,204 @@
   </si>
   <si>
     <t>onlyFSS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
+Freeform and Defined Tags - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Enter subnet name as : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">vcn-name&gt;_&lt;subnet-name&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Source Snapshot:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accepts OCID of the source snapshot  or the name of the key defined under variable  fss_source_ocids in variables_&lt;region&gt;.tf file
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Snapshot Policy - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accepts OCID of the snapshot policy or the name in format: &lt;snaphot_policy_compartment_name&gt;@&lt;snaphost_policy_name&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Replication Information: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Format - TargetFSS(OCID or Name)::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Defined Tags" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -24161,7 +24149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
@@ -24188,9 +24176,9 @@
     <col min="22" max="22" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="157" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="169" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -24204,7 +24192,7 @@
       <c r="K1" s="138"/>
       <c r="L1" s="141"/>
       <c r="M1" s="153" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="N1" s="154"/>
       <c r="O1" s="154"/>
@@ -24216,7 +24204,7 @@
       <c r="U1" s="154"/>
       <c r="V1" s="155"/>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
@@ -24587,7 +24575,7 @@
         <v>88</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="E11" s="56" t="s">
         <v>392</v>
@@ -24626,7 +24614,7 @@
       <c r="G12" s="55"/>
       <c r="H12" s="55"/>
       <c r="I12" s="55" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="J12" s="55"/>
       <c r="K12" s="55"/>
@@ -24648,12 +24636,11 @@
     <mergeCell ref="M1:V1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="B2:C2 A1:A2 E2 D2:D1048576 F2:L1048576 M1:S1048576 U1:XFD1048576" xr:uid="{B7978928-5A58-224D-8649-C886C075337D}"/>
+    <dataValidation allowBlank="1" sqref="M1:S1048576 U1:XFD1048576 D3:D1048576 F3:L1048576 B2:L2 A1:A2" xr:uid="{B7978928-5A58-224D-8649-C886C075337D}"/>
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="T1:T1048576" xr:uid="{0E7A10E6-DADC-0C41-AA06-BB8741B7876C}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D694A32-1E5D-F04E-A872-53BEE2388F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7D14E4-4CC4-FC49-9AF7-9E17EB91AA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5080" yWindow="800" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -670,7 +670,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2791" uniqueCount="1515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2791" uniqueCount="1514">
   <si>
     <t>Region</t>
   </si>
@@ -10655,9 +10655,6 @@
   </si>
   <si>
     <t>Quota Policy</t>
-  </si>
-  <si>
-    <t>ashburn</t>
   </si>
   <si>
     <t>OracleAnalyticsQuota</t>
@@ -19038,7 +19035,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
   </sheetData>
@@ -19071,7 +19068,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="250" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -23942,7 +23939,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -23994,16 +23991,16 @@
         <v>434</v>
       </c>
       <c r="K2" s="29" t="s">
+        <v>1427</v>
+      </c>
+      <c r="L2" s="29" t="s">
         <v>1428</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="M2" s="29" t="s">
         <v>1429</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="N2" s="29" t="s">
         <v>1430</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>1431</v>
       </c>
       <c r="O2" s="29" t="s">
         <v>811</v>
@@ -24069,19 +24066,19 @@
         <v>813</v>
       </c>
       <c r="J4" s="107" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K4" s="107" t="s">
         <v>1432</v>
-      </c>
-      <c r="K4" s="107" t="s">
-        <v>1433</v>
       </c>
       <c r="L4" s="107">
         <v>100</v>
       </c>
       <c r="M4" s="107" t="s">
+        <v>1433</v>
+      </c>
+      <c r="N4" s="107" t="s">
         <v>1434</v>
-      </c>
-      <c r="N4" s="107" t="s">
-        <v>1435</v>
       </c>
       <c r="O4" s="88" t="b">
         <v>1</v>
@@ -24099,7 +24096,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C5" s="55" t="s">
         <v>398</v>
@@ -24178,7 +24175,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="169" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -24192,7 +24189,7 @@
       <c r="K1" s="138"/>
       <c r="L1" s="141"/>
       <c r="M1" s="153" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="N1" s="154"/>
       <c r="O1" s="154"/>
@@ -24233,13 +24230,13 @@
         <v>113</v>
       </c>
       <c r="J2" s="29" t="s">
+        <v>1436</v>
+      </c>
+      <c r="K2" s="29" t="s">
         <v>1437</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="L2" s="29" t="s">
         <v>1438</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>1439</v>
       </c>
       <c r="M2" s="29" t="s">
         <v>114</v>
@@ -24263,10 +24260,10 @@
         <v>120</v>
       </c>
       <c r="T2" s="29" t="s">
+        <v>1439</v>
+      </c>
+      <c r="U2" s="29" t="s">
         <v>1440</v>
-      </c>
-      <c r="U2" s="29" t="s">
-        <v>1441</v>
       </c>
       <c r="V2" s="29" t="s">
         <v>424</v>
@@ -24575,7 +24572,7 @@
         <v>88</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="E11" s="56" t="s">
         <v>392</v>
@@ -24614,7 +24611,7 @@
       <c r="G12" s="55"/>
       <c r="H12" s="55"/>
       <c r="I12" s="55" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="J12" s="55"/>
       <c r="K12" s="55"/>
@@ -27298,13 +27295,13 @@
         <v>828</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="E4" s="56" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G4" s="56" t="b">
         <v>1</v>
@@ -27774,10 +27771,10 @@
         <v>827</v>
       </c>
       <c r="G2" s="29" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H2" s="29" t="s">
         <v>1442</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>1443</v>
       </c>
       <c r="I2" s="29" t="s">
         <v>158</v>
@@ -27841,7 +27838,7 @@
         <v>10000</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
@@ -27875,7 +27872,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="56" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -27892,10 +27889,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="56" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H6" s="56" t="s">
         <v>1446</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>1447</v>
       </c>
       <c r="I6" s="56">
         <v>53</v>
@@ -27905,7 +27902,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="56" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
   </sheetData>
@@ -32058,49 +32055,49 @@
         <v>555</v>
       </c>
       <c r="C3" s="34" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>1449</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="E3" s="34" t="s">
         <v>1450</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="34" t="s">
         <v>1451</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="G3" s="34" t="s">
         <v>1452</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="H3" s="34" t="s">
         <v>1453</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>1454</v>
       </c>
       <c r="I3" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="K3" s="34">
         <v>16</v>
       </c>
       <c r="L3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="M3" t="s">
         <v>1456</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1457</v>
       </c>
       <c r="N3" s="34">
         <v>3</v>
       </c>
       <c r="O3" s="34" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="P3" s="34" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="34" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="R3" s="30"/>
     </row>
@@ -32112,18 +32109,18 @@
         <v>555</v>
       </c>
       <c r="C4" s="34" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>1460</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>1461</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
       <c r="G4" s="34" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>1453</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>1454</v>
       </c>
       <c r="I4" s="34" t="s">
         <v>56</v>
@@ -32140,7 +32137,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="34" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="P4" s="34" t="b">
         <v>0</v>
@@ -32223,7 +32220,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="150" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B1" s="159"/>
       <c r="C1" s="159"/>
@@ -32289,43 +32286,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C3" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>1464</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="E3" s="34" t="s">
         <v>1465</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="34" t="s">
         <v>1466</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="G3" s="34" t="s">
         <v>1467</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="H3" s="34" t="s">
         <v>1468</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="I3" s="34" t="s">
         <v>1469</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="J3" s="34" t="s">
         <v>1470</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="K3" s="34" t="s">
         <v>1471</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="L3" s="34" t="s">
         <v>1472</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="M3" s="34" t="s">
         <v>1473</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="N3" s="34" t="s">
         <v>1474</v>
-      </c>
-      <c r="N3" s="34" t="s">
-        <v>1475</v>
       </c>
       <c r="O3" s="130"/>
     </row>
@@ -32334,41 +32331,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="C4" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>1464</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>1465</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G4" s="34" t="s">
         <v>1467</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="H4" s="34" t="s">
         <v>1468</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="I4" s="34" t="s">
         <v>1469</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="J4" s="34" t="s">
         <v>1470</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="K4" s="34" t="s">
         <v>1471</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="L4" s="34" t="s">
         <v>1472</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="M4" s="34" t="s">
         <v>1473</v>
       </c>
-      <c r="M4" s="34" t="s">
-        <v>1474</v>
-      </c>
       <c r="N4" s="34" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="O4" s="130"/>
     </row>
@@ -33789,7 +33786,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="136" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -33798,7 +33795,7 @@
       <c r="F1" s="136"/>
       <c r="G1" s="136"/>
       <c r="H1" s="146" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="I1" s="136"/>
       <c r="J1" s="136"/>
@@ -33813,46 +33810,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C2" s="132" t="s">
         <v>1481</v>
       </c>
-      <c r="C2" s="132" t="s">
+      <c r="D2" s="17" t="s">
         <v>1482</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>1483</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H2" s="97" t="s">
+        <v>1487</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>1488</v>
+      </c>
+      <c r="J2" s="133" t="s">
+        <v>1489</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>1490</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M2" s="134" t="s">
+        <v>1492</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>1484</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>1486</v>
-      </c>
-      <c r="G2" s="51" t="s">
-        <v>1487</v>
-      </c>
-      <c r="H2" s="97" t="s">
-        <v>1488</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>1489</v>
-      </c>
-      <c r="J2" s="133" t="s">
-        <v>1490</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>1491</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>1492</v>
-      </c>
-      <c r="M2" s="134" t="s">
+      <c r="O2" s="17" t="s">
         <v>1493</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>1485</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -33882,23 +33879,23 @@
         <v>560</v>
       </c>
       <c r="C4" s="34" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>1495</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>1496</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34" t="s">
         <v>560</v>
       </c>
       <c r="G4" s="34" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>1497</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="I4" s="34" t="s">
         <v>1498</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>1499</v>
       </c>
       <c r="J4" s="135">
         <v>256</v>
@@ -33919,19 +33916,19 @@
         <v>555</v>
       </c>
       <c r="G5" s="34" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H5" s="34" t="s">
         <v>1500</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="I5" s="34" t="s">
         <v>1501</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>1502</v>
       </c>
       <c r="J5" s="135">
         <v>384</v>
       </c>
       <c r="K5" s="34" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="L5" s="34"/>
       <c r="M5" s="135"/>
@@ -33946,10 +33943,10 @@
         <v>560</v>
       </c>
       <c r="C6" s="34" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>1504</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>1505</v>
       </c>
       <c r="E6" s="34" t="s">
         <v>5</v>
@@ -33958,13 +33955,13 @@
         <v>560</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="J6" s="135">
         <v>128</v>
@@ -33989,13 +33986,13 @@
         <v>555</v>
       </c>
       <c r="G7" s="34" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H7" s="34" t="s">
         <v>1500</v>
       </c>
-      <c r="H7" s="34" t="s">
-        <v>1501</v>
-      </c>
       <c r="I7" s="34" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="J7" s="135">
         <v>3072</v>
@@ -34016,19 +34013,19 @@
         <v>557</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="J8" s="135">
         <v>521</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="L8" s="34" t="b">
         <v>1</v>
@@ -46773,16 +46770,16 @@
     </row>
     <row r="3" spans="1:5" ht="112" x14ac:dyDescent="0.2">
       <c r="A3" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="66" t="s">
         <v>1395</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="C3" s="66" t="s">
         <v>1396</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="D3" s="34" t="s">
         <v>1397</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>1398</v>
       </c>
       <c r="E3" s="35"/>
     </row>
@@ -46821,7 +46818,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="42" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="136" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -46848,34 +46845,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="114" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E2" s="115" t="s">
         <v>1400</v>
       </c>
-      <c r="E2" s="115" t="s">
+      <c r="F2" s="115" t="s">
         <v>1401</v>
       </c>
-      <c r="F2" s="115" t="s">
+      <c r="G2" s="115" t="s">
         <v>1402</v>
       </c>
-      <c r="G2" s="115" t="s">
+      <c r="H2" s="116" t="s">
         <v>1403</v>
       </c>
-      <c r="H2" s="116" t="s">
+      <c r="I2" s="117" t="s">
         <v>1404</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="J2" s="117" t="s">
         <v>1405</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="K2" s="115" t="s">
         <v>1406</v>
       </c>
-      <c r="K2" s="115" t="s">
+      <c r="L2" s="115" t="s">
         <v>1407</v>
       </c>
-      <c r="L2" s="115" t="s">
+      <c r="M2" s="115" t="s">
         <v>1408</v>
-      </c>
-      <c r="M2" s="115" t="s">
-        <v>1409</v>
       </c>
       <c r="N2" s="118" t="s">
         <v>424</v>
@@ -46883,32 +46880,32 @@
     </row>
     <row r="3" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
       <c r="B3" s="34" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>1410</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="D3" s="34" t="s">
         <v>1411</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>1412</v>
       </c>
       <c r="E3" s="34" t="s">
         <v>401</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G3" s="34">
         <v>10</v>
       </c>
       <c r="H3" s="119"/>
       <c r="I3" s="120" t="s">
+        <v>1413</v>
+      </c>
+      <c r="J3" s="120" t="s">
         <v>1414</v>
-      </c>
-      <c r="J3" s="120" t="s">
-        <v>1415</v>
       </c>
       <c r="K3" s="34"/>
       <c r="L3" s="34"/>
@@ -46917,22 +46914,22 @@
     </row>
     <row r="4" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="34" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
       <c r="B4" s="34" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>1416</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="D4" s="34" t="s">
         <v>1417</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="E4" s="34" t="s">
         <v>1418</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="F4" s="34" t="s">
         <v>1419</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>1420</v>
       </c>
       <c r="G4" s="34">
         <v>100</v>
@@ -46943,7 +46940,7 @@
       <c r="I4" s="120"/>
       <c r="J4" s="120"/>
       <c r="K4" s="34" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="L4" s="121"/>
       <c r="M4" s="34"/>
@@ -46961,13 +46958,13 @@
       <c r="I5" s="120"/>
       <c r="J5" s="120"/>
       <c r="K5" s="34" t="s">
+        <v>1421</v>
+      </c>
+      <c r="L5" s="35" t="s">
         <v>1422</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="M5" s="34" t="s">
         <v>1423</v>
-      </c>
-      <c r="M5" s="34" t="s">
-        <v>1424</v>
       </c>
       <c r="N5" s="122"/>
     </row>
@@ -46983,10 +46980,10 @@
       <c r="I6" s="120"/>
       <c r="J6" s="120"/>
       <c r="K6" s="34" t="s">
+        <v>1424</v>
+      </c>
+      <c r="L6" s="35" t="s">
         <v>1425</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>1426</v>
       </c>
       <c r="M6" s="34"/>
       <c r="N6" s="122"/>

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7D14E4-4CC4-FC49-9AF7-9E17EB91AA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AE2969-80A4-6648-8D5B-9B5E237FEC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10671,265 +10671,6 @@
 </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
-"Region" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Home Region only</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Scope" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Compartment or Tag</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Target" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Compartment Name or {tagNamespace}.{tagKey}.{tagValue}. Note- It should be a </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cost Tracking Tag.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Schedule" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MONTH or  SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Amount" - T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Start Day" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Budget Start Date"/"Budget End Date" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Rules" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Recipients": </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> comma seperated email addresses
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Defined Tags"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                                </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>Scope</t>
   </si>
   <si>
@@ -12761,6 +12502,254 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
+"Region" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Home Region only</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Scope" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment or Tag</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Target" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment Name or {tagNamespace}.{tagKey}.{tagValue}.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Schedule" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MONTH or  SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Amount" - T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Start Day" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Budget Start Date"/"Budget End Date" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Rules" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Recipients": </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> comma seperated email addresses
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Defined Tags"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                                </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -19035,7 +19024,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
   </sheetData>
@@ -19068,7 +19057,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="250" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -23939,7 +23928,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -23991,16 +23980,16 @@
         <v>434</v>
       </c>
       <c r="K2" s="29" t="s">
+        <v>1426</v>
+      </c>
+      <c r="L2" s="29" t="s">
         <v>1427</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="M2" s="29" t="s">
         <v>1428</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="N2" s="29" t="s">
         <v>1429</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>1430</v>
       </c>
       <c r="O2" s="29" t="s">
         <v>811</v>
@@ -24066,19 +24055,19 @@
         <v>813</v>
       </c>
       <c r="J4" s="107" t="s">
+        <v>1430</v>
+      </c>
+      <c r="K4" s="107" t="s">
         <v>1431</v>
-      </c>
-      <c r="K4" s="107" t="s">
-        <v>1432</v>
       </c>
       <c r="L4" s="107">
         <v>100</v>
       </c>
       <c r="M4" s="107" t="s">
+        <v>1432</v>
+      </c>
+      <c r="N4" s="107" t="s">
         <v>1433</v>
-      </c>
-      <c r="N4" s="107" t="s">
-        <v>1434</v>
       </c>
       <c r="O4" s="88" t="b">
         <v>1</v>
@@ -24096,7 +24085,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="C5" s="55" t="s">
         <v>398</v>
@@ -24175,7 +24164,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="169" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -24189,7 +24178,7 @@
       <c r="K1" s="138"/>
       <c r="L1" s="141"/>
       <c r="M1" s="153" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="N1" s="154"/>
       <c r="O1" s="154"/>
@@ -24230,13 +24219,13 @@
         <v>113</v>
       </c>
       <c r="J2" s="29" t="s">
+        <v>1435</v>
+      </c>
+      <c r="K2" s="29" t="s">
         <v>1436</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="L2" s="29" t="s">
         <v>1437</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>1438</v>
       </c>
       <c r="M2" s="29" t="s">
         <v>114</v>
@@ -24260,10 +24249,10 @@
         <v>120</v>
       </c>
       <c r="T2" s="29" t="s">
+        <v>1438</v>
+      </c>
+      <c r="U2" s="29" t="s">
         <v>1439</v>
-      </c>
-      <c r="U2" s="29" t="s">
-        <v>1440</v>
       </c>
       <c r="V2" s="29" t="s">
         <v>424</v>
@@ -24572,7 +24561,7 @@
         <v>88</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="E11" s="56" t="s">
         <v>392</v>
@@ -24611,7 +24600,7 @@
       <c r="G12" s="55"/>
       <c r="H12" s="55"/>
       <c r="I12" s="55" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J12" s="55"/>
       <c r="K12" s="55"/>
@@ -27295,13 +27284,13 @@
         <v>828</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="E4" s="56" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="G4" s="56" t="b">
         <v>1</v>
@@ -27771,10 +27760,10 @@
         <v>827</v>
       </c>
       <c r="G2" s="29" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H2" s="29" t="s">
         <v>1441</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>1442</v>
       </c>
       <c r="I2" s="29" t="s">
         <v>158</v>
@@ -27838,7 +27827,7 @@
         <v>10000</v>
       </c>
       <c r="L4" s="56" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
@@ -27872,7 +27861,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="56" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -27889,10 +27878,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="56" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H6" s="56" t="s">
         <v>1445</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>1446</v>
       </c>
       <c r="I6" s="56">
         <v>53</v>
@@ -27902,7 +27891,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="56" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
@@ -32055,49 +32044,49 @@
         <v>555</v>
       </c>
       <c r="C3" s="34" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>1448</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="E3" s="34" t="s">
         <v>1449</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="34" t="s">
         <v>1450</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="G3" s="34" t="s">
         <v>1451</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="H3" s="34" t="s">
         <v>1452</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>1453</v>
       </c>
       <c r="I3" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="K3" s="34">
         <v>16</v>
       </c>
       <c r="L3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="M3" t="s">
         <v>1455</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1456</v>
       </c>
       <c r="N3" s="34">
         <v>3</v>
       </c>
       <c r="O3" s="34" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="P3" s="34" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="34" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="R3" s="30"/>
     </row>
@@ -32109,18 +32098,18 @@
         <v>555</v>
       </c>
       <c r="C4" s="34" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>1459</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>1460</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
       <c r="G4" s="34" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>1452</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>1453</v>
       </c>
       <c r="I4" s="34" t="s">
         <v>56</v>
@@ -32137,7 +32126,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="34" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="P4" s="34" t="b">
         <v>0</v>
@@ -32220,7 +32209,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="150" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B1" s="159"/>
       <c r="C1" s="159"/>
@@ -32286,43 +32275,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C3" s="34" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>1463</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="E3" s="34" t="s">
         <v>1464</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="34" t="s">
         <v>1465</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="G3" s="34" t="s">
         <v>1466</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="H3" s="34" t="s">
         <v>1467</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="I3" s="34" t="s">
         <v>1468</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="J3" s="34" t="s">
         <v>1469</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="K3" s="34" t="s">
         <v>1470</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="L3" s="34" t="s">
         <v>1471</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="M3" s="34" t="s">
         <v>1472</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="N3" s="34" t="s">
         <v>1473</v>
-      </c>
-      <c r="N3" s="34" t="s">
-        <v>1474</v>
       </c>
       <c r="O3" s="130"/>
     </row>
@@ -32331,41 +32320,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C4" s="34" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>1463</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>1464</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G4" s="34" t="s">
         <v>1466</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="H4" s="34" t="s">
         <v>1467</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="I4" s="34" t="s">
         <v>1468</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="J4" s="34" t="s">
         <v>1469</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="K4" s="34" t="s">
         <v>1470</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="L4" s="34" t="s">
         <v>1471</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="M4" s="34" t="s">
         <v>1472</v>
       </c>
-      <c r="M4" s="34" t="s">
-        <v>1473</v>
-      </c>
       <c r="N4" s="34" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="O4" s="130"/>
     </row>
@@ -33786,7 +33775,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="136" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -33795,7 +33784,7 @@
       <c r="F1" s="136"/>
       <c r="G1" s="136"/>
       <c r="H1" s="146" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="I1" s="136"/>
       <c r="J1" s="136"/>
@@ -33810,46 +33799,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C2" s="132" t="s">
         <v>1480</v>
       </c>
-      <c r="C2" s="132" t="s">
+      <c r="D2" s="17" t="s">
         <v>1481</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>1482</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H2" s="97" t="s">
+        <v>1486</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>1487</v>
+      </c>
+      <c r="J2" s="133" t="s">
+        <v>1488</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>1489</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>1490</v>
+      </c>
+      <c r="M2" s="134" t="s">
+        <v>1491</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>1483</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>1485</v>
-      </c>
-      <c r="G2" s="51" t="s">
-        <v>1486</v>
-      </c>
-      <c r="H2" s="97" t="s">
-        <v>1487</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>1488</v>
-      </c>
-      <c r="J2" s="133" t="s">
-        <v>1489</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>1490</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>1491</v>
-      </c>
-      <c r="M2" s="134" t="s">
+      <c r="O2" s="17" t="s">
         <v>1492</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>1484</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -33879,23 +33868,23 @@
         <v>560</v>
       </c>
       <c r="C4" s="34" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>1494</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>1495</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34" t="s">
         <v>560</v>
       </c>
       <c r="G4" s="34" t="s">
+        <v>1495</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>1496</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="I4" s="34" t="s">
         <v>1497</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>1498</v>
       </c>
       <c r="J4" s="135">
         <v>256</v>
@@ -33916,19 +33905,19 @@
         <v>555</v>
       </c>
       <c r="G5" s="34" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H5" s="34" t="s">
         <v>1499</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="I5" s="34" t="s">
         <v>1500</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>1501</v>
       </c>
       <c r="J5" s="135">
         <v>384</v>
       </c>
       <c r="K5" s="34" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="L5" s="34"/>
       <c r="M5" s="135"/>
@@ -33943,10 +33932,10 @@
         <v>560</v>
       </c>
       <c r="C6" s="34" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>1503</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>1504</v>
       </c>
       <c r="E6" s="34" t="s">
         <v>5</v>
@@ -33955,13 +33944,13 @@
         <v>560</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="J6" s="135">
         <v>128</v>
@@ -33986,13 +33975,13 @@
         <v>555</v>
       </c>
       <c r="G7" s="34" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H7" s="34" t="s">
         <v>1499</v>
       </c>
-      <c r="H7" s="34" t="s">
-        <v>1500</v>
-      </c>
       <c r="I7" s="34" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="J7" s="135">
         <v>3072</v>
@@ -34013,19 +34002,19 @@
         <v>557</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="J8" s="135">
         <v>521</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="L8" s="34" t="b">
         <v>1</v>
@@ -46818,7 +46807,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="42" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="136" t="s">
-        <v>1398</v>
+        <v>1513</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -46845,34 +46834,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="114" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E2" s="115" t="s">
         <v>1399</v>
       </c>
-      <c r="E2" s="115" t="s">
+      <c r="F2" s="115" t="s">
         <v>1400</v>
       </c>
-      <c r="F2" s="115" t="s">
+      <c r="G2" s="115" t="s">
         <v>1401</v>
       </c>
-      <c r="G2" s="115" t="s">
+      <c r="H2" s="116" t="s">
         <v>1402</v>
       </c>
-      <c r="H2" s="116" t="s">
+      <c r="I2" s="117" t="s">
         <v>1403</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="J2" s="117" t="s">
         <v>1404</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="K2" s="115" t="s">
         <v>1405</v>
       </c>
-      <c r="K2" s="115" t="s">
+      <c r="L2" s="115" t="s">
         <v>1406</v>
       </c>
-      <c r="L2" s="115" t="s">
+      <c r="M2" s="115" t="s">
         <v>1407</v>
-      </c>
-      <c r="M2" s="115" t="s">
-        <v>1408</v>
       </c>
       <c r="N2" s="118" t="s">
         <v>424</v>
@@ -46883,29 +46872,29 @@
         <v>5</v>
       </c>
       <c r="B3" s="34" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>1409</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="D3" s="34" t="s">
         <v>1410</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>1411</v>
       </c>
       <c r="E3" s="34" t="s">
         <v>401</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G3" s="34">
         <v>10</v>
       </c>
       <c r="H3" s="119"/>
       <c r="I3" s="120" t="s">
+        <v>1412</v>
+      </c>
+      <c r="J3" s="120" t="s">
         <v>1413</v>
-      </c>
-      <c r="J3" s="120" t="s">
-        <v>1414</v>
       </c>
       <c r="K3" s="34"/>
       <c r="L3" s="34"/>
@@ -46917,19 +46906,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="34" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>1415</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="D4" s="34" t="s">
         <v>1416</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="E4" s="34" t="s">
         <v>1417</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="F4" s="34" t="s">
         <v>1418</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>1419</v>
       </c>
       <c r="G4" s="34">
         <v>100</v>
@@ -46940,7 +46929,7 @@
       <c r="I4" s="120"/>
       <c r="J4" s="120"/>
       <c r="K4" s="34" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="L4" s="121"/>
       <c r="M4" s="34"/>
@@ -46958,13 +46947,13 @@
       <c r="I5" s="120"/>
       <c r="J5" s="120"/>
       <c r="K5" s="34" t="s">
+        <v>1420</v>
+      </c>
+      <c r="L5" s="35" t="s">
         <v>1421</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="M5" s="34" t="s">
         <v>1422</v>
-      </c>
-      <c r="M5" s="34" t="s">
-        <v>1423</v>
       </c>
       <c r="N5" s="122"/>
     </row>
@@ -46980,10 +46969,10 @@
       <c r="I6" s="120"/>
       <c r="J6" s="120"/>
       <c r="K6" s="34" t="s">
+        <v>1423</v>
+      </c>
+      <c r="L6" s="35" t="s">
         <v>1424</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>1425</v>
       </c>
       <c r="M6" s="34"/>
       <c r="N6" s="122"/>

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blohumi/Documents/orahub/cd3-automation-toolkit/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C636EDC-2358-404B-AD08-4EC87815D064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBDECBE-9131-CD41-BD10-9EDB518A524E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5660" yWindow="760" windowWidth="30240" windowHeight="17480" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17480" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -13433,9 +13433,6 @@
     <t>adw</t>
   </si>
   <si>
-    <t>Oracle GUA IPv6 Enabled</t>
-  </si>
-  <si>
     <t>ULA IPv6 CIDR</t>
   </si>
   <si>
@@ -13902,6 +13899,9 @@
       <t xml:space="preserve">
 </t>
     </r>
+  </si>
+  <si>
+    <t>Is Oracle GUA Allocation Enabled</t>
   </si>
 </sst>
 </file>
@@ -20226,7 +20226,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
   </sheetData>
@@ -20264,7 +20264,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="146" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B1" s="147"/>
       <c r="C1" s="147"/>
@@ -20297,13 +20297,13 @@
         <v>782</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>1604</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>1605</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>1606</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>12</v>
@@ -20347,7 +20347,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="G3" s="33"/>
       <c r="H3" s="33" t="s">
@@ -21188,7 +21188,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>39</v>
@@ -21253,7 +21253,7 @@
         <v>49</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>50</v>
@@ -28379,10 +28379,10 @@
         <v>5</v>
       </c>
       <c r="B13" s="32" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>1611</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>1612</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="33"/>
@@ -52452,7 +52452,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="40" customFormat="1" ht="131" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="142" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -52525,21 +52525,21 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>394</v>
       </c>
       <c r="D5" s="32" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>1615</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>1616</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="I5" s="33"/>
     </row>
@@ -52549,7 +52549,7 @@
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -52562,7 +52562,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -52919,7 +52919,7 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -53311,7 +53311,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="32" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32"/>
@@ -53323,7 +53323,7 @@
       <c r="C69" s="32"/>
       <c r="D69" s="32"/>
       <c r="E69" s="32" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
@@ -53335,7 +53335,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="32" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32"/>
@@ -53347,7 +53347,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="32" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
@@ -53359,7 +53359,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="32"/>
       <c r="E72" s="32" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
@@ -53371,7 +53371,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
@@ -53383,7 +53383,7 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="32" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -53395,7 +53395,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="32" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32"/>
@@ -53407,7 +53407,7 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="32" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32"/>
@@ -53419,7 +53419,7 @@
       <c r="C77" s="32"/>
       <c r="D77" s="32"/>
       <c r="E77" s="32" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32"/>
@@ -54099,7 +54099,7 @@
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="F131" s="32"/>
       <c r="G131" s="32"/>
@@ -54111,7 +54111,7 @@
       <c r="C132" s="32"/>
       <c r="D132" s="32"/>
       <c r="E132" s="32" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="F132" s="32"/>
       <c r="G132" s="32"/>
@@ -54775,7 +54775,7 @@
       <c r="C186" s="32"/>
       <c r="D186" s="32"/>
       <c r="E186" s="32" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="F186" s="32"/>
       <c r="G186" s="32"/>
@@ -54787,7 +54787,7 @@
       <c r="C187" s="32"/>
       <c r="D187" s="32"/>
       <c r="E187" s="32" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="F187" s="32"/>
       <c r="G187" s="32"/>
@@ -54799,7 +54799,7 @@
       <c r="C188" s="32"/>
       <c r="D188" s="32"/>
       <c r="E188" s="32" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F188" s="32"/>
       <c r="G188" s="32"/>
@@ -55331,7 +55331,7 @@
       <c r="C231" s="32"/>
       <c r="D231" s="32"/>
       <c r="E231" s="32" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="F231" s="32"/>
       <c r="G231" s="32"/>
@@ -55457,7 +55457,7 @@
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
       <c r="E242" s="32" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="F242" s="33"/>
       <c r="G242" s="33"/>
@@ -55469,7 +55469,7 @@
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
       <c r="E243" s="32" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="F243" s="33"/>
       <c r="G243" s="33"/>
@@ -55481,7 +55481,7 @@
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
       <c r="E244" s="32" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="F244" s="33"/>
       <c r="G244" s="33"/>

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blohumi/Documents/orahub/cd3-automation-toolkit/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBDECBE-9131-CD41-BD10-9EDB518A524E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AC5EC7-2DC5-5A4C-A876-75EE02BD02DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17480" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB2FB4F-20F7-EA48-AFB1-22C107B761BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E8874D-F262-2640-92FD-8B9ABC9B6DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17440" tabRatio="1000" firstSheet="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -803,7 +803,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="1657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="1658">
   <si>
     <t>Region</t>
   </si>
@@ -13816,6 +13816,9 @@
       <t xml:space="preserve">
 Updated Instances sheet, Exa-Infra sheet</t>
     </r>
+  </si>
+  <si>
+    <t>Plugin OS Management Service Agent</t>
   </si>
 </sst>
 </file>
@@ -14831,6 +14834,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -14909,8 +14914,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -20163,25 +20166,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1635</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="142" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="144" t="s">
         <v>1524</v>
       </c>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="144"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="146"/>
     </row>
     <row r="2" spans="1:15" s="40" customFormat="1" ht="45" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -20536,19 +20539,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1525</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="148" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="150" t="s">
         <v>1031</v>
       </c>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
     </row>
     <row r="2" spans="1:9" ht="16">
       <c r="A2" s="26" t="s">
@@ -20719,10 +20722,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="40" customFormat="1" ht="95.25" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1023</v>
       </c>
-      <c r="B1" s="147"/>
+      <c r="B1" s="149"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="26" t="s">
@@ -20789,16 +20792,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="103.75" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1024</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
     </row>
     <row r="2" spans="1:8" s="40" customFormat="1" ht="43.5" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -21042,31 +21045,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="205" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1019</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="149" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="151" t="s">
         <v>1020</v>
       </c>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:21" s="40" customFormat="1" ht="59.5" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -22255,18 +22258,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="63" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1025</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
     </row>
     <row r="2" spans="1:10" ht="29.25" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -22381,17 +22384,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1026</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="7" t="s">
@@ -22487,25 +22490,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1027</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="7" t="s">
@@ -22643,28 +22646,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="140" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1028</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="138"/>
-      <c r="S1" s="138"/>
-      <c r="T1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
     </row>
     <row r="2" spans="1:20" ht="16">
       <c r="A2" s="47" t="s">
@@ -23642,17 +23645,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="175" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1008</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="4" t="s">
@@ -24039,13 +24042,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="108" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1021</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="26" t="s">
@@ -24302,19 +24305,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="203.25" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="153" t="s">
         <v>1009</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
     </row>
     <row r="2" spans="1:11" ht="32">
       <c r="A2" s="26" t="s">
@@ -24489,15 +24492,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="102" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1029</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
     </row>
     <row r="2" spans="1:7" s="40" customFormat="1" ht="28.75" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -24648,7 +24651,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.1640625" customWidth="1"/>
@@ -24678,56 +24681,58 @@
     <col min="26" max="26" width="17.6640625" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="16.6640625" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="14.1640625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="6.1640625" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14" customWidth="1"/>
-    <col min="36" max="36" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="8.1640625" customWidth="1"/>
+    <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14" customWidth="1"/>
+    <col min="37" max="37" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="321" customHeight="1">
-      <c r="A1" s="153" t="s">
+    <row r="1" spans="1:37" ht="321" customHeight="1">
+      <c r="A1" s="155" t="s">
         <v>1527</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="138" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="140" t="s">
         <v>1637</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="140"/>
-      <c r="AD1" s="140"/>
-      <c r="AE1" s="140"/>
-      <c r="AF1" s="140"/>
-      <c r="AG1" s="140"/>
-      <c r="AH1" s="140"/>
-      <c r="AI1" s="140"/>
-      <c r="AJ1" s="141"/>
-    </row>
-    <row r="2" spans="1:36" s="40" customFormat="1" ht="52.5" customHeight="1">
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="142"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="142"/>
+      <c r="V1" s="142"/>
+      <c r="W1" s="142"/>
+      <c r="X1" s="142"/>
+      <c r="Y1" s="142"/>
+      <c r="Z1" s="142"/>
+      <c r="AA1" s="142"/>
+      <c r="AB1" s="142"/>
+      <c r="AC1" s="142"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="142"/>
+      <c r="AF1" s="142"/>
+      <c r="AG1" s="142"/>
+      <c r="AH1" s="142"/>
+      <c r="AI1" s="142"/>
+      <c r="AJ1" s="142"/>
+      <c r="AK1" s="143"/>
+    </row>
+    <row r="2" spans="1:37" s="40" customFormat="1" ht="52.5" customHeight="1">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -24813,31 +24818,34 @@
         <v>1650</v>
       </c>
       <c r="AC2" s="27" t="s">
+        <v>1657</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1651</v>
       </c>
-      <c r="AD2" s="26" t="s">
+      <c r="AE2" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="AE2" s="26" t="s">
+      <c r="AF2" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="AF2" s="27" t="s">
+      <c r="AG2" s="27" t="s">
         <v>545</v>
       </c>
-      <c r="AG2" s="26" t="s">
+      <c r="AH2" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="AH2" s="27" t="s">
+      <c r="AI2" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="AI2" s="27" t="s">
+      <c r="AJ2" s="27" t="s">
         <v>956</v>
       </c>
-      <c r="AJ2" s="26" t="s">
+      <c r="AK2" s="26" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="42" customHeight="1">
+    <row r="3" spans="1:37" ht="42" customHeight="1">
       <c r="A3" s="33" t="s">
         <v>313</v>
       </c>
@@ -24865,7 +24873,7 @@
       <c r="I3" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="J3" s="168" t="s">
+      <c r="J3" s="138" t="s">
         <v>1654</v>
       </c>
       <c r="K3" s="33">
@@ -24889,19 +24897,20 @@
       <c r="AA3" s="33"/>
       <c r="AB3" s="33"/>
       <c r="AC3" s="33"/>
-      <c r="AD3" s="33" t="s">
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="AE3" s="33" t="s">
+      <c r="AF3" s="33" t="s">
         <v>682</v>
       </c>
-      <c r="AF3" s="33"/>
       <c r="AG3" s="33"/>
       <c r="AH3" s="33"/>
       <c r="AI3" s="33"/>
       <c r="AJ3" s="33"/>
-    </row>
-    <row r="4" spans="1:36" ht="28.75" customHeight="1">
+      <c r="AK3" s="33"/>
+    </row>
+    <row r="4" spans="1:37" ht="28.75" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
@@ -24926,15 +24935,15 @@
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
       <c r="V4" s="33"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="33"/>
+      <c r="AE4" s="6"/>
       <c r="AF4" s="33"/>
-      <c r="AG4" s="6"/>
+      <c r="AG4" s="33"/>
       <c r="AH4" s="6"/>
       <c r="AI4" s="6"/>
-      <c r="AJ4" s="33"/>
-    </row>
-    <row r="5" spans="1:36" ht="128">
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="33"/>
+    </row>
+    <row r="5" spans="1:37" ht="80">
       <c r="A5" s="53" t="s">
         <v>5</v>
       </c>
@@ -24986,27 +24995,28 @@
       <c r="AA5" s="53"/>
       <c r="AB5" s="53"/>
       <c r="AC5" s="53"/>
-      <c r="AD5" s="53" t="s">
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="AE5" s="53" t="s">
+      <c r="AF5" s="53" t="s">
         <v>1655</v>
       </c>
-      <c r="AF5" s="53" t="s">
+      <c r="AG5" s="53" t="s">
         <v>361</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53" t="s">
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="AI5" s="54" t="s">
+      <c r="AJ5" s="54" t="s">
         <v>1048</v>
       </c>
-      <c r="AJ5" s="54" t="s">
+      <c r="AK5" s="54" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="96">
+    <row r="6" spans="1:37" ht="48">
       <c r="A6" s="53" t="s">
         <v>5</v>
       </c>
@@ -25032,18 +25042,18 @@
       <c r="I6" s="53" t="s">
         <v>430</v>
       </c>
-      <c r="J6" s="169" t="s">
+      <c r="J6" s="139" t="s">
         <v>102</v>
       </c>
-      <c r="K6" s="169">
+      <c r="K6" s="139">
         <v>16</v>
       </c>
-      <c r="L6" s="169">
+      <c r="L6" s="139">
         <v>55</v>
       </c>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
+      <c r="M6" s="139"/>
+      <c r="N6" s="139"/>
+      <c r="O6" s="139"/>
       <c r="P6" s="53"/>
       <c r="Q6" s="53"/>
       <c r="R6" s="53"/>
@@ -25058,23 +25068,24 @@
       <c r="AA6" s="53"/>
       <c r="AB6" s="53"/>
       <c r="AC6" s="53"/>
-      <c r="AD6" s="53" t="s">
+      <c r="AD6" s="53"/>
+      <c r="AE6" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="AE6" s="53" t="s">
+      <c r="AF6" s="53" t="s">
         <v>386</v>
       </c>
-      <c r="AF6" s="53"/>
-      <c r="AG6" s="53" t="s">
+      <c r="AG6" s="53"/>
+      <c r="AH6" s="53" t="s">
         <v>384</v>
       </c>
-      <c r="AH6" s="53"/>
-      <c r="AI6" s="54" t="s">
+      <c r="AI6" s="53"/>
+      <c r="AJ6" s="54" t="s">
         <v>1049</v>
       </c>
-      <c r="AJ6" s="53"/>
-    </row>
-    <row r="7" spans="1:36" ht="96">
+      <c r="AK6" s="53"/>
+    </row>
+    <row r="7" spans="1:37" ht="48">
       <c r="A7" s="53" t="s">
         <v>5</v>
       </c>
@@ -25100,14 +25111,14 @@
       <c r="I7" s="53" t="s">
         <v>429</v>
       </c>
-      <c r="J7" s="169" t="s">
+      <c r="J7" s="139" t="s">
         <v>102</v>
       </c>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="M7" s="139"/>
+      <c r="N7" s="139"/>
+      <c r="O7" s="139"/>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="53"/>
@@ -25122,21 +25133,22 @@
       <c r="AA7" s="53"/>
       <c r="AB7" s="53"/>
       <c r="AC7" s="53"/>
-      <c r="AD7" s="53" t="s">
+      <c r="AD7" s="53"/>
+      <c r="AE7" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="AE7" s="53" t="s">
+      <c r="AF7" s="53" t="s">
         <v>386</v>
       </c>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="53" t="s">
+      <c r="AG7" s="53"/>
+      <c r="AH7" s="53" t="s">
         <v>385</v>
       </c>
-      <c r="AH7" s="53"/>
       <c r="AI7" s="53"/>
       <c r="AJ7" s="53"/>
-    </row>
-    <row r="8" spans="1:36" ht="96">
+      <c r="AK7" s="53"/>
+    </row>
+    <row r="8" spans="1:37" ht="48">
       <c r="A8" s="53" t="s">
         <v>5</v>
       </c>
@@ -25162,14 +25174,14 @@
       <c r="I8" s="53" t="s">
         <v>853</v>
       </c>
-      <c r="J8" s="169" t="s">
+      <c r="J8" s="139" t="s">
         <v>102</v>
       </c>
-      <c r="K8" s="169"/>
-      <c r="L8" s="169"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="139"/>
       <c r="P8" s="53"/>
       <c r="Q8" s="53"/>
       <c r="R8" s="53"/>
@@ -25184,27 +25196,28 @@
       <c r="AA8" s="53"/>
       <c r="AB8" s="53"/>
       <c r="AC8" s="53"/>
-      <c r="AD8" s="53" t="s">
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="AE8" s="53" t="s">
+      <c r="AF8" s="53" t="s">
         <v>386</v>
       </c>
-      <c r="AF8" s="53"/>
-      <c r="AG8" s="53" t="s">
+      <c r="AG8" s="53"/>
+      <c r="AH8" s="53" t="s">
         <v>385</v>
       </c>
-      <c r="AH8" s="53"/>
       <c r="AI8" s="53"/>
       <c r="AJ8" s="53"/>
+      <c r="AK8" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:AJ1"/>
+    <mergeCell ref="I1:AK1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="E1:XFD2 A1:C2 AD9:AJ1048576 H3:P1048576 D1:D1048576 AK3:XFD1048576 S3:AC1048576 AD3:AD8 AG3:AJ8" xr:uid="{49F95CF8-626F-B943-836C-F0AE33F8148B}"/>
+    <dataValidation allowBlank="1" sqref="E1:XFD2 A1:C2 AE9:AK1048576 H3:P1048576 D1:D1048576 AL3:XFD1048576 S3:AD1048576 AE3:AE8 AH3:AK8" xr:uid="{49F95CF8-626F-B943-836C-F0AE33F8148B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -25243,26 +25256,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="207" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1522</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="144"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="145"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="146"/>
     </row>
     <row r="2" spans="1:18" s="40" customFormat="1" ht="62" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -25501,32 +25514,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="169" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1191</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="156" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="158" t="s">
         <v>1187</v>
       </c>
-      <c r="N1" s="157"/>
-      <c r="O1" s="157"/>
-      <c r="P1" s="157"/>
-      <c r="Q1" s="157"/>
-      <c r="R1" s="157"/>
-      <c r="S1" s="157"/>
-      <c r="T1" s="157"/>
-      <c r="U1" s="157"/>
-      <c r="V1" s="158"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
+      <c r="R1" s="159"/>
+      <c r="S1" s="159"/>
+      <c r="T1" s="159"/>
+      <c r="U1" s="159"/>
+      <c r="V1" s="160"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -26039,45 +26052,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1192</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="153" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="155" t="s">
         <v>1222</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="154"/>
-      <c r="AA1" s="154"/>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="154"/>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="154"/>
-      <c r="AH1" s="154"/>
-      <c r="AI1" s="154"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="156"/>
+      <c r="AG1" s="156"/>
+      <c r="AH1" s="156"/>
+      <c r="AI1" s="156"/>
     </row>
     <row r="2" spans="1:35" s="1" customFormat="1" ht="43" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -26530,27 +26543,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1193</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="138"/>
-      <c r="S1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
     </row>
     <row r="2" spans="1:19" ht="43" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -26828,30 +26841,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="123" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="144"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="145"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="146"/>
     </row>
     <row r="2" spans="1:22" ht="58.5" customHeight="1">
       <c r="A2" s="34" t="s">
@@ -27181,25 +27194,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="122.25" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1030</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1">
       <c r="A2" s="8" t="s">
@@ -27455,29 +27468,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="159" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>424</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="145" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="147" t="s">
         <v>435</v>
       </c>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
-      <c r="O1" s="159"/>
-      <c r="P1" s="159"/>
-      <c r="Q1" s="159"/>
-      <c r="R1" s="159"/>
-      <c r="S1" s="160"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="161"/>
+      <c r="S1" s="162"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1">
       <c r="A2" s="8" t="s">
@@ -28181,15 +28194,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="40" customFormat="1" ht="105.75" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="141" t="s">
         <v>1224</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="143"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="105" t="s">
@@ -28491,14 +28504,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="44.5" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="147"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -28645,12 +28658,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="151" t="s">
         <v>1195</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="143"/>
     </row>
     <row r="2" spans="1:4" ht="79" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -28752,22 +28765,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>802</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="144"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="146"/>
     </row>
     <row r="2" spans="1:14" ht="58" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -29311,20 +29324,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>802</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
     </row>
     <row r="2" spans="1:12" ht="72.75" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -29539,28 +29552,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1584</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="138"/>
-      <c r="S1" s="138"/>
-      <c r="T1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
     </row>
     <row r="2" spans="1:20" ht="53" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -29940,35 +29953,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="146.25" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1201</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="143"/>
-      <c r="Z1" s="143"/>
-      <c r="AA1" s="144"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="145"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="145"/>
+      <c r="Z1" s="145"/>
+      <c r="AA1" s="146"/>
     </row>
     <row r="2" spans="1:27" s="48" customFormat="1" ht="48">
       <c r="A2" s="49" t="s">
@@ -33332,16 +33345,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>1018</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
     </row>
     <row r="2" spans="1:8" ht="48">
       <c r="A2" s="66" t="s">
@@ -33490,29 +33503,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="155" t="s">
         <v>1202</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
       <c r="V1" s="71"/>
       <c r="W1" s="71"/>
       <c r="X1" s="71"/>
@@ -33764,26 +33777,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="170.25" customHeight="1">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="163" t="s">
         <v>1523</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="162"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="162"/>
-      <c r="R1" s="163"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
+      <c r="M1" s="164"/>
+      <c r="N1" s="164"/>
+      <c r="O1" s="164"/>
+      <c r="P1" s="164"/>
+      <c r="Q1" s="164"/>
+      <c r="R1" s="165"/>
       <c r="S1" s="12"/>
     </row>
     <row r="2" spans="1:19" s="48" customFormat="1" ht="72.75" customHeight="1">
@@ -34036,22 +34049,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="155" t="s">
         <v>1203</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
+      <c r="M1" s="164"/>
+      <c r="N1" s="164"/>
     </row>
     <row r="2" spans="1:15" s="40" customFormat="1" ht="16">
       <c r="A2" s="35" t="s">
@@ -34273,16 +34286,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="166" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1264</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="143"/>
     </row>
     <row r="2" spans="1:8" ht="14.5" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -35263,26 +35276,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="281.25" customHeight="1">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="166" t="s">
         <v>1016</v>
       </c>
-      <c r="B1" s="165"/>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
-      <c r="L1" s="165"/>
-      <c r="M1" s="165"/>
-      <c r="N1" s="165"/>
-      <c r="O1" s="165"/>
-      <c r="P1" s="165"/>
-      <c r="Q1" s="165"/>
-      <c r="R1" s="166"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="167"/>
+      <c r="N1" s="167"/>
+      <c r="O1" s="167"/>
+      <c r="P1" s="167"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="168"/>
     </row>
     <row r="2" spans="1:18" ht="48">
       <c r="A2" s="26" t="s">
@@ -35636,25 +35649,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1526</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="149" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="151" t="s">
         <v>1158</v>
       </c>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
     </row>
     <row r="2" spans="1:15" ht="44" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -36941,39 +36954,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="169" t="s">
         <v>1528</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="163"/>
-      <c r="I1" s="153" t="s">
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="155" t="s">
         <v>1529</v>
       </c>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="154"/>
-      <c r="AA1" s="154"/>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="154"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
     </row>
     <row r="2" spans="1:29" s="40" customFormat="1" ht="48">
       <c r="A2" s="35" t="s">
@@ -43216,16 +43229,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1569</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
       <c r="I1" s="133"/>
       <c r="J1" s="1"/>
     </row>
@@ -52373,14 +52386,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="134.25" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1058</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="143"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="26" t="s">
@@ -52445,16 +52458,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="40" customFormat="1" ht="131" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1608</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
     </row>
     <row r="2" spans="1:9" s="40" customFormat="1">
       <c r="A2" s="136" t="s">
@@ -56108,19 +56121,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="168" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="144" t="s">
         <v>704</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="145" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="147" t="s">
         <v>1022</v>
       </c>
-      <c r="H1" s="146"/>
-      <c r="I1" s="147"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="149"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="37" t="s">
@@ -56485,13 +56498,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="92" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1081</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="105" t="s">
@@ -56575,22 +56588,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="40" customFormat="1" ht="207" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1190</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="143"/>
     </row>
     <row r="2" spans="1:14" ht="16">
       <c r="A2" s="105" t="s">

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E8874D-F262-2640-92FD-8B9ABC9B6DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501B0411-0BDA-2449-A70F-3B6588EE0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -803,7 +803,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="1658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="1657">
   <si>
     <t>Region</t>
   </si>
@@ -13216,9 +13216,6 @@
   </si>
   <si>
     <t>Allow group AccessGovernanceAdmins to inspect all-resources in tenancy</t>
-  </si>
-  <si>
-    <t>Oracle-Tags.CreatedOn=2025-09-25T11:07:41.577Z;Oracle-Tags.CreatedBy=oracleidentitycloudservice/ulaganathan.namachivayam@oracle.com</t>
   </si>
   <si>
     <t>Allow group AccessGovernanceAdmins to read policies in tenancy</t>
@@ -20129,7 +20126,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="79" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
   </sheetData>
@@ -20167,7 +20164,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -20200,7 +20197,7 @@
         <v>782</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="F2" s="15" t="s">
         <v>1601</v>
@@ -24701,7 +24698,7 @@
       <c r="G1" s="156"/>
       <c r="H1" s="157"/>
       <c r="I1" s="140" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="J1" s="142"/>
       <c r="K1" s="142"/>
@@ -24776,52 +24773,52 @@
         <v>790</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>1057</v>
       </c>
       <c r="Q2" s="27" t="s">
+        <v>1638</v>
+      </c>
+      <c r="R2" s="27" t="s">
         <v>1639</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="S2" s="27" t="s">
         <v>1640</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="T2" s="27" t="s">
         <v>1641</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="27" t="s">
         <v>1642</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1643</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1644</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>1645</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>1646</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1647</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1648</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>1649</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1650</v>
-      </c>
-      <c r="AC2" s="27" t="s">
-        <v>1657</v>
-      </c>
-      <c r="AD2" s="27" t="s">
-        <v>1651</v>
       </c>
       <c r="AE2" s="26" t="s">
         <v>92</v>
@@ -24862,19 +24859,19 @@
         <v>346</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="G3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>428</v>
       </c>
       <c r="J3" s="138" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="K3" s="33">
         <v>8</v>
@@ -25000,7 +24997,7 @@
         <v>100</v>
       </c>
       <c r="AF5" s="53" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="AG5" s="53" t="s">
         <v>361</v>
@@ -52457,7 +52454,7 @@
     <col min="8" max="8" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="40" customFormat="1" ht="131" customHeight="1">
+    <row r="1" spans="1:8" s="40" customFormat="1" ht="131" customHeight="1">
       <c r="A1" s="140" t="s">
         <v>1608</v>
       </c>
@@ -52469,7 +52466,7 @@
       <c r="G1" s="140"/>
       <c r="H1" s="140"/>
     </row>
-    <row r="2" spans="1:9" s="40" customFormat="1">
+    <row r="2" spans="1:8" s="40" customFormat="1">
       <c r="A2" s="136" t="s">
         <v>0</v>
       </c>
@@ -52495,7 +52492,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="69.75" customHeight="1">
+    <row r="3" spans="1:8" ht="69.75" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
@@ -52515,7 +52512,7 @@
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
     </row>
-    <row r="4" spans="1:9" ht="69.75" customHeight="1">
+    <row r="4" spans="1:8" ht="69.75" customHeight="1">
       <c r="A4" s="32"/>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
@@ -52527,7 +52524,7 @@
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
     </row>
-    <row r="5" spans="1:9" ht="80">
+    <row r="5" spans="1:8" ht="48">
       <c r="A5" s="32" t="s">
         <v>5</v>
       </c>
@@ -52545,38 +52542,33 @@
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
-      <c r="H5" s="32" t="s">
-        <v>1612</v>
-      </c>
-      <c r="I5" s="33"/>
-    </row>
-    <row r="6" spans="1:9" ht="32">
+      <c r="H5" s="32"/>
+    </row>
+    <row r="6" spans="1:8" ht="32">
       <c r="A6" s="32"/>
       <c r="B6" s="32"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="33"/>
-    </row>
-    <row r="7" spans="1:9" ht="32">
+    </row>
+    <row r="7" spans="1:8" ht="32">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="33"/>
-    </row>
-    <row r="8" spans="1:9" ht="102.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:8" ht="102.75" customHeight="1">
       <c r="A8" s="32" t="s">
         <v>5</v>
       </c>
@@ -52596,7 +52588,7 @@
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
     </row>
-    <row r="9" spans="1:9" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="32"/>
       <c r="B9" s="32"/>
       <c r="C9" s="32"/>
@@ -52608,7 +52600,7 @@
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:9" ht="29.25" customHeight="1">
+    <row r="10" spans="1:8" ht="29.25" customHeight="1">
       <c r="A10" s="32"/>
       <c r="B10" s="32"/>
       <c r="C10" s="32"/>
@@ -52620,7 +52612,7 @@
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
     </row>
-    <row r="11" spans="1:9" ht="29.25" customHeight="1">
+    <row r="11" spans="1:8" ht="29.25" customHeight="1">
       <c r="A11" s="32"/>
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>
@@ -52632,7 +52624,7 @@
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
     </row>
-    <row r="12" spans="1:9" ht="29.25" customHeight="1">
+    <row r="12" spans="1:8" ht="29.25" customHeight="1">
       <c r="A12" s="32"/>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -52644,7 +52636,7 @@
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
     </row>
-    <row r="13" spans="1:9" ht="29.25" customHeight="1">
+    <row r="13" spans="1:8" ht="29.25" customHeight="1">
       <c r="A13" s="32"/>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -52656,7 +52648,7 @@
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
     </row>
-    <row r="14" spans="1:9" ht="29.25" customHeight="1">
+    <row r="14" spans="1:8" ht="29.25" customHeight="1">
       <c r="A14" s="32"/>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
@@ -52668,7 +52660,7 @@
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
     </row>
-    <row r="15" spans="1:9" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="32"/>
       <c r="B15" s="32"/>
       <c r="C15" s="32"/>
@@ -52680,7 +52672,7 @@
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
     </row>
-    <row r="16" spans="1:9" ht="29.25" customHeight="1">
+    <row r="16" spans="1:8" ht="29.25" customHeight="1">
       <c r="A16" s="32"/>
       <c r="B16" s="32"/>
       <c r="C16" s="32"/>
@@ -52926,7 +52918,7 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -53318,7 +53310,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="32" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32"/>
@@ -53330,7 +53322,7 @@
       <c r="C69" s="32"/>
       <c r="D69" s="32"/>
       <c r="E69" s="32" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
@@ -53342,7 +53334,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="32" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32"/>
@@ -53354,7 +53346,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="32" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
@@ -53366,7 +53358,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="32"/>
       <c r="E72" s="32" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
@@ -53378,7 +53370,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
@@ -53390,7 +53382,7 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="32" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -53402,7 +53394,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="32" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32"/>
@@ -53414,7 +53406,7 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="32" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32"/>
@@ -53426,7 +53418,7 @@
       <c r="C77" s="32"/>
       <c r="D77" s="32"/>
       <c r="E77" s="32" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32"/>
@@ -54106,7 +54098,7 @@
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="F131" s="32"/>
       <c r="G131" s="32"/>
@@ -54118,7 +54110,7 @@
       <c r="C132" s="32"/>
       <c r="D132" s="32"/>
       <c r="E132" s="32" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="F132" s="32"/>
       <c r="G132" s="32"/>
@@ -54782,7 +54774,7 @@
       <c r="C186" s="32"/>
       <c r="D186" s="32"/>
       <c r="E186" s="32" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F186" s="32"/>
       <c r="G186" s="32"/>
@@ -54794,7 +54786,7 @@
       <c r="C187" s="32"/>
       <c r="D187" s="32"/>
       <c r="E187" s="32" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="F187" s="32"/>
       <c r="G187" s="32"/>
@@ -54806,7 +54798,7 @@
       <c r="C188" s="32"/>
       <c r="D188" s="32"/>
       <c r="E188" s="32" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="F188" s="32"/>
       <c r="G188" s="32"/>
@@ -55338,7 +55330,7 @@
       <c r="C231" s="32"/>
       <c r="D231" s="32"/>
       <c r="E231" s="32" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="F231" s="32"/>
       <c r="G231" s="32"/>
@@ -55464,7 +55456,7 @@
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
       <c r="E242" s="32" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="F242" s="33"/>
       <c r="G242" s="33"/>
@@ -55476,7 +55468,7 @@
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
       <c r="E243" s="32" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="F243" s="33"/>
       <c r="G243" s="33"/>
@@ -55488,7 +55480,7 @@
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
       <c r="E244" s="32" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="F244" s="33"/>
       <c r="G244" s="33"/>

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501B0411-0BDA-2449-A70F-3B6588EE0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C27474C-C124-3D4E-A4EF-387844BB7914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -803,7 +803,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="1657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="1656">
   <si>
     <t>Region</t>
   </si>
@@ -4344,21 +4344,6 @@
     <t>Chicago</t>
   </si>
   <si>
-    <t>gov-ashburn</t>
-  </si>
-  <si>
-    <t>gov-cardiff</t>
-  </si>
-  <si>
-    <t>gov-chicago</t>
-  </si>
-  <si>
-    <t>gov-london</t>
-  </si>
-  <si>
-    <t>gov-phoenix</t>
-  </si>
-  <si>
     <t>Jerusalem</t>
   </si>
   <si>
@@ -13816,6 +13801,18 @@
   </si>
   <si>
     <t>Plugin OS Management Service Agent</t>
+  </si>
+  <si>
+    <t>ashburn</t>
+  </si>
+  <si>
+    <t>chicago</t>
+  </si>
+  <si>
+    <t>london</t>
+  </si>
+  <si>
+    <t>cardiff</t>
   </si>
 </sst>
 </file>
@@ -20126,7 +20123,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="79" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
     </row>
   </sheetData>
@@ -20164,7 +20161,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -20175,7 +20172,7 @@
       <c r="H1" s="145"/>
       <c r="I1" s="146"/>
       <c r="J1" s="144" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="K1" s="145"/>
       <c r="L1" s="145"/>
@@ -20197,13 +20194,13 @@
         <v>782</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>12</v>
@@ -20247,7 +20244,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="G3" s="33"/>
       <c r="H3" s="33" t="s">
@@ -20537,7 +20534,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -20545,7 +20542,7 @@
       <c r="E1" s="140"/>
       <c r="F1" s="140"/>
       <c r="G1" s="150" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="H1" s="150"/>
       <c r="I1" s="150"/>
@@ -20564,7 +20561,7 @@
         <v>636</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>637</v>
@@ -20628,13 +20625,13 @@
         <v>570</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
@@ -20648,16 +20645,16 @@
         <v>347</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
@@ -20720,7 +20717,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="40" customFormat="1" ht="95.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B1" s="149"/>
     </row>
@@ -20790,7 +20787,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="103.75" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -21043,7 +21040,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="205" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -21055,7 +21052,7 @@
       <c r="I1" s="145"/>
       <c r="J1" s="146"/>
       <c r="K1" s="151" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="L1" s="151"/>
       <c r="M1" s="151"/>
@@ -21082,13 +21079,13 @@
         <v>309</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>39</v>
@@ -21153,7 +21150,7 @@
         <v>49</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>50</v>
@@ -21741,13 +21738,13 @@
         <v>572</v>
       </c>
       <c r="D14" s="53" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53" t="s">
@@ -21758,7 +21755,7 @@
       </c>
       <c r="J14" s="53"/>
       <c r="K14" s="53" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="L14" s="53"/>
       <c r="M14" s="54" t="s">
@@ -21797,13 +21794,13 @@
         <v>572</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="E15" s="53" t="s">
+        <v>915</v>
+      </c>
+      <c r="F15" s="53" t="s">
         <v>920</v>
-      </c>
-      <c r="F15" s="53" t="s">
-        <v>925</v>
       </c>
       <c r="G15" s="53"/>
       <c r="H15" s="53" t="s">
@@ -21814,7 +21811,7 @@
       </c>
       <c r="J15" s="53"/>
       <c r="K15" s="53" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="L15" s="53"/>
       <c r="M15" s="53"/>
@@ -22256,7 +22253,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="63" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -22382,7 +22379,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -22488,7 +22485,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -22644,7 +22641,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="140" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -23643,7 +23640,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="175" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="B1" s="152"/>
       <c r="C1" s="152"/>
@@ -23662,22 +23659,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>922</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>924</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>925</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>926</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>927</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>928</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>929</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>930</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>931</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>417</v>
@@ -23704,19 +23701,19 @@
         <v>347</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="H4" s="32">
         <v>3600</v>
@@ -23731,19 +23728,19 @@
         <v>347</v>
       </c>
       <c r="C5" s="32" t="s">
+        <v>927</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>928</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>932</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="F5" s="32" t="s">
         <v>933</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>937</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>938</v>
-      </c>
       <c r="G5" s="32" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="H5" s="32">
         <v>300</v>
@@ -23758,19 +23755,19 @@
         <v>347</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="H6" s="32">
         <v>300</v>
@@ -24040,7 +24037,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="108" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -24072,7 +24069,7 @@
         <v>548</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>394</v>
@@ -24087,7 +24084,7 @@
         <v>549</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>394</v>
@@ -24096,13 +24093,13 @@
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1">
       <c r="A5" s="32" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>347</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>394</v>
@@ -24117,7 +24114,7 @@
         <v>550</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>394</v>
@@ -24303,7 +24300,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="203.25" customHeight="1">
       <c r="A1" s="153" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="B1" s="154"/>
       <c r="C1" s="154"/>
@@ -24330,22 +24327,22 @@
         <v>309</v>
       </c>
       <c r="E2" s="26" t="s">
+        <v>939</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>940</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>941</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>942</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>943</v>
+      </c>
+      <c r="J2" s="26" t="s">
         <v>944</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>945</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>946</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>947</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>948</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>949</v>
       </c>
       <c r="K2" s="26" t="s">
         <v>417</v>
@@ -24380,20 +24377,20 @@
         <v>569</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="G4" s="33" t="s">
         <v>781</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="I4" s="28"/>
       <c r="J4" s="29" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="K4" s="29"/>
     </row>
@@ -24411,16 +24408,16 @@
         <v>571</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="G5" s="33" t="s">
         <v>575</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="I5" s="29"/>
       <c r="J5" s="29"/>
@@ -24490,7 +24487,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="102" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -24688,7 +24685,7 @@
   <sheetData>
     <row r="1" spans="1:37" ht="321" customHeight="1">
       <c r="A1" s="155" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="B1" s="156"/>
       <c r="C1" s="156"/>
@@ -24698,7 +24695,7 @@
       <c r="G1" s="156"/>
       <c r="H1" s="157"/>
       <c r="I1" s="140" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="J1" s="142"/>
       <c r="K1" s="142"/>
@@ -24746,7 +24743,7 @@
         <v>83</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>89</v>
@@ -24773,52 +24770,52 @@
         <v>790</v>
       </c>
       <c r="O2" s="27" t="s">
+        <v>1632</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>1052</v>
+      </c>
+      <c r="Q2" s="27" t="s">
+        <v>1633</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>1634</v>
+      </c>
+      <c r="S2" s="27" t="s">
+        <v>1635</v>
+      </c>
+      <c r="T2" s="27" t="s">
+        <v>1636</v>
+      </c>
+      <c r="U2" s="27" t="s">
         <v>1637</v>
       </c>
-      <c r="P2" s="27" t="s">
-        <v>1057</v>
-      </c>
-      <c r="Q2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1638</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1639</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>1640</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>1641</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1642</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1643</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>1644</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
+        <v>1651</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1645</v>
-      </c>
-      <c r="Y2" s="27" t="s">
-        <v>1646</v>
-      </c>
-      <c r="Z2" s="27" t="s">
-        <v>1647</v>
-      </c>
-      <c r="AA2" s="27" t="s">
-        <v>1648</v>
-      </c>
-      <c r="AB2" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="AC2" s="27" t="s">
-        <v>1656</v>
-      </c>
-      <c r="AD2" s="27" t="s">
-        <v>1650</v>
       </c>
       <c r="AE2" s="26" t="s">
         <v>92</v>
@@ -24836,7 +24833,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" s="27" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="AK2" s="26" t="s">
         <v>417</v>
@@ -24859,19 +24856,19 @@
         <v>346</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="G3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>1652</v>
+        <v>1647</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>428</v>
       </c>
       <c r="J3" s="138" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
       <c r="K3" s="33">
         <v>8</v>
@@ -24957,7 +24954,7 @@
         <v>101</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="G5" s="53" t="b">
         <v>0</v>
@@ -24976,7 +24973,7 @@
       </c>
       <c r="N5" s="53"/>
       <c r="O5" s="53" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="P5" s="53"/>
       <c r="Q5" s="53"/>
@@ -24997,7 +24994,7 @@
         <v>100</v>
       </c>
       <c r="AF5" s="53" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="AG5" s="53" t="s">
         <v>361</v>
@@ -25007,7 +25004,7 @@
         <v>88</v>
       </c>
       <c r="AJ5" s="54" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="AK5" s="54" t="s">
         <v>426</v>
@@ -25030,7 +25027,7 @@
         <v>346</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -25078,7 +25075,7 @@
       </c>
       <c r="AI6" s="53"/>
       <c r="AJ6" s="54" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="AK6" s="53"/>
     </row>
@@ -25099,7 +25096,7 @@
         <v>101</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="G7" s="53" t="b">
         <v>0</v>
@@ -25162,7 +25159,7 @@
         <v>346</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="G8" s="53" t="b">
         <v>0</v>
@@ -25254,7 +25251,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="207" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -25285,7 +25282,7 @@
         <v>103</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>104</v>
@@ -25306,16 +25303,16 @@
         <v>427</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="O2" s="27" t="s">
         <v>791</v>
@@ -25381,19 +25378,19 @@
         <v>793</v>
       </c>
       <c r="J4" s="100" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="K4" s="100" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="L4" s="100">
         <v>100</v>
       </c>
       <c r="M4" s="100" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="N4" s="100" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="O4" s="82" t="b">
         <v>1</v>
@@ -25411,7 +25408,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="C5" s="53" t="s">
         <v>391</v>
@@ -25512,7 +25509,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="169" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -25526,7 +25523,7 @@
       <c r="K1" s="145"/>
       <c r="L1" s="146"/>
       <c r="M1" s="158" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="N1" s="159"/>
       <c r="O1" s="159"/>
@@ -25552,7 +25549,7 @@
         <v>108</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>109</v>
@@ -25567,13 +25564,13 @@
         <v>111</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="M2" s="27" t="s">
         <v>112</v>
@@ -25597,10 +25594,10 @@
         <v>118</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="U2" s="27" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="V2" s="27" t="s">
         <v>417</v>
@@ -25614,7 +25611,7 @@
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
       <c r="E3" s="32" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="F3" s="33"/>
       <c r="G3" s="33"/>
@@ -25648,7 +25645,7 @@
         <v>119</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
@@ -25752,7 +25749,7 @@
         <v>119</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
@@ -25790,7 +25787,7 @@
         <v>127</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="53"/>
       <c r="G8" s="53"/>
@@ -25832,7 +25829,7 @@
         <v>130</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F9" s="53"/>
       <c r="G9" s="53"/>
@@ -25874,7 +25871,7 @@
         <v>132</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F10" s="53"/>
       <c r="G10" s="53"/>
@@ -25909,10 +25906,10 @@
         <v>87</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F11" s="53"/>
       <c r="G11" s="53"/>
@@ -25948,7 +25945,7 @@
       <c r="G12" s="53"/>
       <c r="H12" s="53"/>
       <c r="I12" s="53" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
@@ -26050,7 +26047,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -26067,7 +26064,7 @@
       <c r="N1" s="145"/>
       <c r="O1" s="146"/>
       <c r="P1" s="155" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="Q1" s="156"/>
       <c r="R1" s="156"/>
@@ -26100,7 +26097,7 @@
         <v>854</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>855</v>
@@ -26112,10 +26109,10 @@
         <v>857</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="J2" s="27" t="s">
         <v>858</v>
@@ -26130,7 +26127,7 @@
         <v>861</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O2" s="27" t="s">
         <v>862</v>
@@ -26154,13 +26151,13 @@
         <v>864</v>
       </c>
       <c r="V2" s="27" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="W2" s="27" t="s">
         <v>81</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="Y2" s="27" t="s">
         <v>865</v>
@@ -26169,7 +26166,7 @@
         <v>866</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="AB2" s="27" t="s">
         <v>867</v>
@@ -26187,13 +26184,13 @@
         <v>869</v>
       </c>
       <c r="AG2" s="27" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="AH2" s="27" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="AI2" s="27" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1">
@@ -26246,10 +26243,10 @@
         <v>870</v>
       </c>
       <c r="D4" s="92" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="F4" s="92" t="s">
         <v>872</v>
@@ -26258,10 +26255,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="92" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="I4" s="92" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="J4" s="54" t="b">
         <v>0</v>
@@ -26276,10 +26273,10 @@
         <v>882</v>
       </c>
       <c r="N4" s="92" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="O4" s="92" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="P4" s="92">
         <v>1</v>
@@ -26300,13 +26297,13 @@
         <v>884</v>
       </c>
       <c r="V4" s="92" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="W4" s="92" t="s">
         <v>96</v>
       </c>
       <c r="X4" s="92" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="Y4" s="92"/>
       <c r="Z4" s="92"/>
@@ -26341,10 +26338,10 @@
       <c r="L5" s="54"/>
       <c r="M5" s="54"/>
       <c r="N5" s="54" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="O5" s="92" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="P5" s="54">
         <v>2</v>
@@ -26363,13 +26360,13 @@
       </c>
       <c r="U5" s="54"/>
       <c r="V5" s="92" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="W5" s="54" t="s">
         <v>87</v>
       </c>
       <c r="X5" s="92" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="Y5" s="54"/>
       <c r="Z5" s="54"/>
@@ -26398,10 +26395,10 @@
         <v>880</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="F6" s="54" t="s">
         <v>881</v>
@@ -26410,10 +26407,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="92" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="I6" s="92" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="J6" s="54" t="b">
         <v>0</v>
@@ -26422,10 +26419,10 @@
       <c r="L6" s="54"/>
       <c r="M6" s="54"/>
       <c r="N6" s="54" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="O6" s="92" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="P6" s="54">
         <v>1</v>
@@ -26446,20 +26443,20 @@
         <v>884</v>
       </c>
       <c r="V6" s="92" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="W6" s="54" t="s">
         <v>96</v>
       </c>
       <c r="X6" s="92" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="Y6" s="54">
         <v>2</v>
       </c>
       <c r="Z6" s="54"/>
       <c r="AA6" s="92" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="AB6" s="94"/>
       <c r="AC6" s="54" t="s">
@@ -26471,7 +26468,7 @@
       <c r="AG6" s="53"/>
       <c r="AH6" s="53"/>
       <c r="AI6" s="54" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
     </row>
   </sheetData>
@@ -26541,7 +26538,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -26582,7 +26579,7 @@
         <v>648</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>135</v>
@@ -26657,7 +26654,7 @@
       <c r="E4" s="53"/>
       <c r="F4" s="53"/>
       <c r="G4" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="H4" s="54" t="b">
         <v>1</v>
@@ -26731,7 +26728,7 @@
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="54" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="H6" s="54" t="b">
         <v>0</v>
@@ -26839,7 +26836,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="123" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -26883,7 +26880,7 @@
         <v>152</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="H2" s="34" t="s">
         <v>153</v>
@@ -26973,7 +26970,7 @@
         <v>163</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="H4" s="53" t="s">
         <v>164</v>
@@ -27033,7 +27030,7 @@
         <v>169</v>
       </c>
       <c r="G5" s="53" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="H5" s="53" t="s">
         <v>164</v>
@@ -27081,7 +27078,7 @@
         <v>172</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="H6" s="53" t="s">
         <v>164</v>
@@ -27192,7 +27189,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="122.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -28097,7 +28094,7 @@
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
       <c r="J23" s="53" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="K23" s="53"/>
       <c r="L23" s="53"/>
@@ -28192,7 +28189,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="40" customFormat="1" ht="105.75" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -28212,10 +28209,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="107" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="E2" s="107" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="F2" s="128" t="s">
         <v>422</v>
@@ -28232,7 +28229,7 @@
         <v>551</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="33"/>
@@ -28247,7 +28244,7 @@
         <v>825</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="33"/>
@@ -28277,7 +28274,7 @@
         <v>554</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33"/>
@@ -28292,7 +28289,7 @@
         <v>555</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="19"/>
@@ -28307,7 +28304,7 @@
         <v>556</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="32"/>
@@ -28322,7 +28319,7 @@
         <v>557</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
@@ -28352,7 +28349,7 @@
         <v>642</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
@@ -28379,10 +28376,10 @@
         <v>5</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="33"/>
@@ -28408,7 +28405,7 @@
         <v>826</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="6"/>
@@ -28425,7 +28422,7 @@
         <v>828</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
@@ -28442,7 +28439,7 @@
         <v>830</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
@@ -28656,7 +28653,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1">
       <c r="A1" s="151" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -28670,10 +28667,10 @@
         <v>134</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="79" customHeight="1">
@@ -28692,10 +28689,10 @@
         <v>392</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="93.5" customHeight="1">
@@ -28706,10 +28703,10 @@
         <v>392</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
     </row>
   </sheetData>
@@ -28790,7 +28787,7 @@
         <v>803</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>816</v>
@@ -28852,13 +28849,13 @@
         <v>806</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="E4" s="54" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="G4" s="54" t="b">
         <v>1</v>
@@ -28890,7 +28887,7 @@
         <v>810</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="E5" s="54" t="b">
         <v>1</v>
@@ -29356,10 +29353,10 @@
         <v>805</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="I2" s="27" t="s">
         <v>155</v>
@@ -29371,7 +29368,7 @@
         <v>438</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="29.25" customHeight="1">
@@ -29423,7 +29420,7 @@
         <v>10000</v>
       </c>
       <c r="L4" s="54" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32">
@@ -29457,7 +29454,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16">
@@ -29474,10 +29471,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="54" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="H6" s="54" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="I6" s="54">
         <v>53</v>
@@ -29487,7 +29484,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="54" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
     </row>
   </sheetData>
@@ -29550,7 +29547,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -29583,10 +29580,10 @@
         <v>844</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="F2" s="15" t="s">
         <v>845</v>
@@ -29601,16 +29598,16 @@
         <v>311</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="N2" s="15" t="s">
         <v>846</v>
@@ -29670,7 +29667,7 @@
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="54" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
@@ -29683,20 +29680,20 @@
         <v>326</v>
       </c>
       <c r="J4" s="53" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="K4" s="53"/>
       <c r="L4" s="53" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="N4" s="53" t="s">
         <v>315</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="P4" s="53" t="s">
         <v>403</v>
@@ -29718,39 +29715,39 @@
         <v>549</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F5" s="54"/>
       <c r="G5" s="54" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="H5" s="54"/>
       <c r="I5" s="135" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="J5" s="54" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="K5" s="54" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="L5" s="54" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="54" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="N5" s="54" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="O5" s="54" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="P5" s="54" t="s">
         <v>322</v>
@@ -29951,7 +29948,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="146.25" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -29991,7 +29988,7 @@
         <v>81</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>709</v>
@@ -30105,7 +30102,7 @@
         <v>55</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="E4" s="87" t="s">
         <v>741</v>
@@ -30180,7 +30177,7 @@
         <v>87</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="E5" s="96" t="s">
         <v>743</v>
@@ -33343,7 +33340,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -33405,7 +33402,7 @@
         <v>55</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="F4" s="54">
         <v>2</v>
@@ -33501,7 +33498,7 @@
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1">
       <c r="A1" s="155" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B1" s="156"/>
       <c r="C1" s="156"/>
@@ -33545,10 +33542,10 @@
         <v>732</v>
       </c>
       <c r="E2" s="66" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="G2" s="66" t="s">
         <v>711</v>
@@ -33563,16 +33560,16 @@
         <v>733</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="N2" s="66" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="O2" s="66" t="s">
         <v>734</v>
@@ -33641,10 +33638,10 @@
         <v>753</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="G4" s="53">
         <v>4</v>
@@ -33668,7 +33665,7 @@
         <v>96</v>
       </c>
       <c r="N4" s="88" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="O4" s="88" t="b">
         <v>1</v>
@@ -33690,7 +33687,7 @@
     </row>
     <row r="11" spans="1:28" ht="16">
       <c r="E11" s="1" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -33775,7 +33772,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="170.25" customHeight="1">
       <c r="A1" s="163" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="B1" s="164"/>
       <c r="C1" s="164"/>
@@ -33804,46 +33801,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="34" t="s">
+        <v>952</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E2" s="119" t="s">
+        <v>953</v>
+      </c>
+      <c r="F2" s="119" t="s">
+        <v>954</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>955</v>
+      </c>
+      <c r="H2" s="119" t="s">
+        <v>956</v>
+      </c>
+      <c r="I2" s="34" t="s">
         <v>957</v>
       </c>
-      <c r="D2" s="34" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E2" s="119" t="s">
+      <c r="J2" s="34" t="s">
         <v>958</v>
       </c>
-      <c r="F2" s="119" t="s">
+      <c r="K2" s="34" t="s">
         <v>959</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="L2" s="120" t="s">
+        <v>1045</v>
+      </c>
+      <c r="M2" s="121" t="s">
+        <v>1046</v>
+      </c>
+      <c r="N2" s="34" t="s">
         <v>960</v>
       </c>
-      <c r="H2" s="119" t="s">
+      <c r="O2" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="P2" s="34" t="s">
         <v>962</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>963</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>964</v>
-      </c>
-      <c r="L2" s="120" t="s">
-        <v>1050</v>
-      </c>
-      <c r="M2" s="121" t="s">
-        <v>1051</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>965</v>
-      </c>
-      <c r="O2" s="34" t="s">
-        <v>966</v>
-      </c>
-      <c r="P2" s="34" t="s">
-        <v>967</v>
       </c>
       <c r="Q2" s="34" t="s">
         <v>92</v>
@@ -33860,49 +33857,49 @@
         <v>548</v>
       </c>
       <c r="C3" s="32" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H3" s="32" t="s">
         <v>1131</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>1132</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>1134</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>1135</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>1136</v>
       </c>
       <c r="I3" s="32" t="s">
         <v>55</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="K3" s="32">
         <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="M3" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="N3" s="32">
         <v>3</v>
       </c>
       <c r="O3" s="32" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="P3" s="32" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="R3" s="28"/>
     </row>
@@ -33914,18 +33911,18 @@
         <v>548</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
       <c r="G4" s="32" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="I4" s="32" t="s">
         <v>55</v>
@@ -33942,7 +33939,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="32" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="P4" s="32" t="b">
         <v>0</v>
@@ -34047,7 +34044,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1">
       <c r="A1" s="155" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B1" s="164"/>
       <c r="C1" s="164"/>
@@ -34068,43 +34065,43 @@
         <v>0</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="C2" s="119" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="D2" s="34" t="s">
+        <v>963</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>964</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>965</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>966</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>967</v>
+      </c>
+      <c r="I2" s="34" t="s">
         <v>968</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="J2" s="34" t="s">
         <v>969</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="K2" s="34" t="s">
         <v>970</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="L2" s="34" t="s">
         <v>971</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="M2" s="34" t="s">
         <v>972</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="N2" s="34" t="s">
         <v>973</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>974</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>975</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>976</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>977</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>978</v>
       </c>
       <c r="O2" s="48"/>
     </row>
@@ -34113,43 +34110,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="D3" s="32" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I3" s="32" t="s">
         <v>1145</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="J3" s="32" t="s">
         <v>1146</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="K3" s="32" t="s">
         <v>1147</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="L3" s="32" t="s">
         <v>1148</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="M3" s="32" t="s">
         <v>1149</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="N3" s="32" t="s">
         <v>1150</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>1153</v>
-      </c>
-      <c r="M3" s="32" t="s">
-        <v>1154</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>1155</v>
       </c>
       <c r="O3" s="122"/>
     </row>
@@ -34158,41 +34155,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>1145</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>1147</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="L4" s="32" t="s">
         <v>1148</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="M4" s="32" t="s">
         <v>1149</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>1150</v>
-      </c>
-      <c r="J4" s="32" t="s">
+      <c r="N4" s="32" t="s">
         <v>1151</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>1153</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>1154</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>1156</v>
       </c>
       <c r="O4" s="122"/>
     </row>
@@ -34284,7 +34281,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="166" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -34299,22 +34296,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="G2" s="129" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>417</v>
@@ -35274,7 +35271,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="281.25" customHeight="1">
       <c r="A1" s="166" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="B1" s="167"/>
       <c r="C1" s="167"/>
@@ -35302,49 +35299,49 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>974</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>975</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>976</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>977</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>978</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>979</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="I2" s="26" t="s">
         <v>980</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="J2" s="26" t="s">
         <v>981</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="K2" s="27" t="s">
         <v>982</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="L2" s="26" t="s">
         <v>983</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="M2" s="27" t="s">
         <v>984</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="N2" s="27" t="s">
         <v>985</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="O2" s="27" t="s">
         <v>986</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>987</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="Q2" s="27" t="s">
         <v>988</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>989</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>990</v>
-      </c>
-      <c r="O2" s="27" t="s">
-        <v>991</v>
-      </c>
-      <c r="P2" s="27" t="s">
-        <v>992</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>993</v>
       </c>
       <c r="R2" s="26" t="s">
         <v>417</v>
@@ -35363,43 +35360,43 @@
         <v>548</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>989</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>990</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>991</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>991</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>992</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>993</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J4" s="28" t="s">
         <v>994</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="K4" s="28" t="s">
         <v>995</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="L4" s="28" t="s">
         <v>996</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>996</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>997</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>998</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>1044</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>999</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>1000</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>1001</v>
       </c>
       <c r="M4" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="O4" s="28" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="P4" s="28"/>
       <c r="Q4" s="28"/>
@@ -35412,40 +35409,40 @@
         <v>548</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="K5" s="28" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="M5" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="O5" s="28"/>
       <c r="P5" s="28"/>
@@ -35459,22 +35456,22 @@
         <v>548</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="I6" s="29"/>
       <c r="J6" s="28"/>
@@ -35494,38 +35491,38 @@
         <v>548</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="J7" s="28"/>
       <c r="K7" s="28" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="L7" s="28" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="M7" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -35647,7 +35644,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -35656,7 +35653,7 @@
       <c r="F1" s="140"/>
       <c r="G1" s="140"/>
       <c r="H1" s="151" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="I1" s="140"/>
       <c r="J1" s="140"/>
@@ -35671,46 +35668,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C2" s="124" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>1159</v>
       </c>
-      <c r="C2" s="124" t="s">
+      <c r="G2" s="49" t="s">
         <v>1160</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="H2" s="91" t="s">
         <v>1161</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>1162</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="J2" s="125" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K2" s="15" t="s">
         <v>1164</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="L2" s="15" t="s">
         <v>1165</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="M2" s="126" t="s">
         <v>1166</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="N2" s="15" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O2" s="15" t="s">
         <v>1167</v>
-      </c>
-      <c r="J2" s="125" t="s">
-        <v>1168</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>1169</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>1170</v>
-      </c>
-      <c r="M2" s="126" t="s">
-        <v>1171</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>1163</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16">
@@ -35740,23 +35737,23 @@
         <v>550</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
         <v>550</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="J4" s="127">
         <v>256</v>
@@ -35777,19 +35774,19 @@
         <v>548</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="J5" s="127">
         <v>384</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="L5" s="32"/>
       <c r="M5" s="127"/>
@@ -35804,10 +35801,10 @@
         <v>550</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>5</v>
@@ -35816,13 +35813,13 @@
         <v>550</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="J6" s="127">
         <v>128</v>
@@ -35847,13 +35844,13 @@
         <v>548</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="H7" s="32" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I7" s="32" t="s">
         <v>1179</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>1184</v>
       </c>
       <c r="J7" s="127">
         <v>3072</v>
@@ -35874,19 +35871,19 @@
         <v>549</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="J8" s="127">
         <v>521</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="L8" s="32" t="b">
         <v>1</v>
@@ -36952,7 +36949,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1">
       <c r="A1" s="169" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="B1" s="164"/>
       <c r="C1" s="164"/>
@@ -36962,7 +36959,7 @@
       <c r="G1" s="164"/>
       <c r="H1" s="165"/>
       <c r="I1" s="155" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="J1" s="156"/>
       <c r="K1" s="156"/>
@@ -36999,10 +36996,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="G2" s="34" t="s">
         <v>81</v>
@@ -37011,64 +37008,64 @@
         <v>83</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="J2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="L2" s="35" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="M2" s="34" t="s">
         <v>90</v>
       </c>
       <c r="N2" s="34" t="s">
+        <v>1529</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>1530</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>1531</v>
+      </c>
+      <c r="Q2" s="34" t="s">
+        <v>1532</v>
+      </c>
+      <c r="R2" s="34" t="s">
+        <v>1533</v>
+      </c>
+      <c r="S2" s="34" t="s">
         <v>1534</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="T2" s="34" t="s">
         <v>1535</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="U2" s="34" t="s">
         <v>1536</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="V2" s="34" t="s">
         <v>1537</v>
       </c>
-      <c r="R2" s="34" t="s">
+      <c r="W2" s="34" t="s">
         <v>1538</v>
       </c>
-      <c r="S2" s="34" t="s">
+      <c r="X2" s="34" t="s">
         <v>1539</v>
       </c>
-      <c r="T2" s="34" t="s">
+      <c r="Y2" s="34" t="s">
         <v>1540</v>
       </c>
-      <c r="U2" s="34" t="s">
+      <c r="Z2" s="34" t="s">
         <v>1541</v>
-      </c>
-      <c r="V2" s="34" t="s">
-        <v>1542</v>
-      </c>
-      <c r="W2" s="34" t="s">
-        <v>1543</v>
-      </c>
-      <c r="X2" s="34" t="s">
-        <v>1544</v>
-      </c>
-      <c r="Y2" s="34" t="s">
-        <v>1545</v>
-      </c>
-      <c r="Z2" s="34" t="s">
-        <v>1546</v>
       </c>
       <c r="AA2" s="34" t="s">
         <v>75</v>
       </c>
       <c r="AB2" s="34" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="AC2" s="35" t="s">
         <v>417</v>
@@ -37115,16 +37112,16 @@
         <v>549</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>55</v>
@@ -37133,58 +37130,58 @@
         <v>346</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="33" t="s">
+        <v>1548</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>1549</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>1550</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>1551</v>
+      </c>
+      <c r="R4" s="18" t="s">
+        <v>1552</v>
+      </c>
+      <c r="S4" s="18" t="s">
         <v>1553</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="T4" s="18" t="s">
         <v>1554</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>1554</v>
-      </c>
-      <c r="P4" s="18" t="s">
-        <v>1555</v>
-      </c>
-      <c r="Q4" s="18" t="s">
-        <v>1556</v>
-      </c>
-      <c r="R4" s="18" t="s">
-        <v>1557</v>
-      </c>
-      <c r="S4" s="18" t="s">
-        <v>1558</v>
-      </c>
-      <c r="T4" s="18" t="s">
-        <v>1559</v>
       </c>
       <c r="U4" s="18" t="s">
         <v>190</v>
       </c>
       <c r="V4" s="18" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="W4" s="18" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="X4" s="132" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="Y4" s="18" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="Z4" s="18" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="AA4" s="18"/>
       <c r="AB4" s="6" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="AC4" s="18"/>
     </row>
@@ -37196,16 +37193,16 @@
         <v>549</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>87</v>
@@ -37214,56 +37211,56 @@
         <v>101</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="K5" s="32"/>
       <c r="L5" s="32"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O5" s="32" t="s">
+        <v>1549</v>
+      </c>
+      <c r="P5" s="32" t="s">
+        <v>1550</v>
+      </c>
+      <c r="Q5" s="32" t="s">
+        <v>1551</v>
+      </c>
+      <c r="R5" s="32" t="s">
+        <v>1552</v>
+      </c>
+      <c r="S5" s="32" t="s">
+        <v>1553</v>
+      </c>
+      <c r="T5" s="32" t="s">
         <v>1554</v>
-      </c>
-      <c r="O5" s="32" t="s">
-        <v>1554</v>
-      </c>
-      <c r="P5" s="32" t="s">
-        <v>1555</v>
-      </c>
-      <c r="Q5" s="32" t="s">
-        <v>1556</v>
-      </c>
-      <c r="R5" s="32" t="s">
-        <v>1557</v>
-      </c>
-      <c r="S5" s="32" t="s">
-        <v>1558</v>
-      </c>
-      <c r="T5" s="32" t="s">
-        <v>1559</v>
       </c>
       <c r="U5" s="32" t="s">
         <v>190</v>
       </c>
       <c r="V5" s="32" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="W5" s="32" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="X5" s="32" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="Y5" s="32" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="Z5" s="32" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="AA5" s="32"/>
       <c r="AB5" s="33" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="AC5" s="32"/>
     </row>
@@ -43227,7 +43224,7 @@
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -43253,13 +43250,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>417</v>
@@ -43282,23 +43279,23 @@
     </row>
     <row r="4" spans="1:81" ht="32" customHeight="1">
       <c r="A4" s="32" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>549</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="H4" s="32"/>
     </row>
@@ -43309,32 +43306,32 @@
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
       <c r="F5" s="32" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="H5" s="32"/>
     </row>
     <row r="6" spans="1:81" ht="32" customHeight="1">
       <c r="A6" s="32" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>549</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="H6" s="32"/>
     </row>
@@ -43345,10 +43342,10 @@
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="H7" s="32"/>
     </row>
@@ -43359,10 +43356,10 @@
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="32" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="H8" s="32"/>
     </row>
@@ -44856,7 +44853,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="F12" s="33"/>
       <c r="H12" s="33" t="s">
@@ -44873,7 +44870,7 @@
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="33" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="F13" s="33"/>
       <c r="H13" s="33" t="s">
@@ -45759,25 +45756,25 @@
         <v>651</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="F1" s="65" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="H1" s="65" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="I1" s="65" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="J1" s="65" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="K1" s="65" t="s">
         <v>653</v>
@@ -45885,13 +45882,13 @@
         <v>886</v>
       </c>
       <c r="AT1" s="56" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="AU1" s="56" t="s">
         <v>652</v>
       </c>
       <c r="AV1" s="56" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="2" spans="1:48" s="58" customFormat="1" ht="16">
@@ -45937,7 +45934,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="130" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="M2" s="59" t="s">
         <v>38</v>
@@ -46472,7 +46469,7 @@
       </c>
       <c r="K6" s="59"/>
       <c r="L6" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -47122,7 +47119,7 @@
       </c>
       <c r="K14" s="59"/>
       <c r="L14" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="M14" s="59"/>
       <c r="N14" s="59"/>
@@ -47196,7 +47193,7 @@
       </c>
       <c r="K15" s="59"/>
       <c r="L15" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="M15" s="59"/>
       <c r="N15" s="59"/>
@@ -47266,7 +47263,7 @@
       </c>
       <c r="K16" s="59"/>
       <c r="L16" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="M16" s="59"/>
       <c r="N16" s="59"/>
@@ -47406,7 +47403,7 @@
       </c>
       <c r="K18" s="59"/>
       <c r="L18" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="M18" s="59"/>
       <c r="N18" s="59"/>
@@ -47476,7 +47473,7 @@
       </c>
       <c r="K19" s="59"/>
       <c r="L19" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="M19" s="59"/>
       <c r="N19" s="59"/>
@@ -47616,7 +47613,7 @@
       </c>
       <c r="K21" s="59"/>
       <c r="L21" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="M21" s="59"/>
       <c r="N21" s="59"/>
@@ -47756,7 +47753,7 @@
       </c>
       <c r="K23" s="59"/>
       <c r="L23" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="M23" s="59"/>
       <c r="N23" s="59"/>
@@ -47896,7 +47893,7 @@
       </c>
       <c r="K25" s="59"/>
       <c r="L25" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="M25" s="59"/>
       <c r="N25" s="59"/>
@@ -48036,7 +48033,7 @@
       </c>
       <c r="K27" s="59"/>
       <c r="L27" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="M27" s="59"/>
       <c r="N27" s="59"/>
@@ -48176,7 +48173,7 @@
       </c>
       <c r="K29" s="59"/>
       <c r="L29" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="M29" s="59"/>
       <c r="N29" s="59"/>
@@ -48246,7 +48243,7 @@
       </c>
       <c r="K30" s="59"/>
       <c r="L30" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="M30" s="59"/>
       <c r="N30" s="59"/>
@@ -48316,7 +48313,7 @@
       </c>
       <c r="K31" s="59"/>
       <c r="L31" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="M31" s="59"/>
       <c r="N31" s="59"/>
@@ -48456,7 +48453,7 @@
       </c>
       <c r="K33" s="59"/>
       <c r="L33" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="M33" s="59"/>
       <c r="N33" s="59"/>
@@ -48596,7 +48593,7 @@
       </c>
       <c r="K35" s="59"/>
       <c r="L35" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="M35" s="59"/>
       <c r="N35" s="59"/>
@@ -48648,7 +48645,7 @@
     <row r="36" spans="1:47" s="58" customFormat="1">
       <c r="K36" s="59"/>
       <c r="L36" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="M36" s="59"/>
       <c r="N36" s="59"/>
@@ -48701,7 +48698,7 @@
       </c>
       <c r="K37" s="59"/>
       <c r="L37" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="M37" s="59"/>
       <c r="N37" s="59"/>
@@ -48981,7 +48978,7 @@
       </c>
       <c r="K41" s="59"/>
       <c r="L41" s="64" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="M41" s="59"/>
       <c r="N41" s="59"/>
@@ -49093,7 +49090,7 @@
         <v>41</v>
       </c>
       <c r="L43" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="P43" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A43,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A43,4,4,1,"DHCP")))</f>
@@ -49179,7 +49176,7 @@
         <v>43</v>
       </c>
       <c r="L45" s="58" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="P45" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P45" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A45,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A45,4,4,1,"DHCP")))</f>
@@ -49222,7 +49219,7 @@
         <v>44</v>
       </c>
       <c r="L46" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="P46" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P46" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A46,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A46,4,4,1,"DHCP")))</f>
@@ -49265,7 +49262,7 @@
         <v>45</v>
       </c>
       <c r="L47" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="P47" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A47,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A47,4,4,1,"DHCP")))</f>
@@ -49308,7 +49305,7 @@
         <v>46</v>
       </c>
       <c r="L48" s="40" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="P48" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A48,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A48,4,4,1,"DHCP")))</f>
@@ -49351,7 +49348,7 @@
         <v>47</v>
       </c>
       <c r="L49" t="s">
-        <v>891</v>
+        <v>1652</v>
       </c>
       <c r="P49" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"DHCP")))</f>
@@ -49394,7 +49391,7 @@
         <v>48</v>
       </c>
       <c r="L50" t="s">
-        <v>893</v>
+        <v>1653</v>
       </c>
       <c r="P50" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"DHCP")))</f>
@@ -49426,7 +49423,7 @@
         <v>49</v>
       </c>
       <c r="L51" t="s">
-        <v>895</v>
+        <v>1568</v>
       </c>
       <c r="AG51" s="64"/>
       <c r="AU51" s="103" t="str">
@@ -49445,7 +49442,7 @@
       <c r="I52" s="58"/>
       <c r="J52" s="58"/>
       <c r="L52" s="40" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="AU52" s="103" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -49464,7 +49461,7 @@
       <c r="I53" s="58"/>
       <c r="J53" s="58"/>
       <c r="L53" t="s">
-        <v>894</v>
+        <v>1654</v>
       </c>
       <c r="AU53" s="103" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -49483,7 +49480,7 @@
       <c r="I54" s="58"/>
       <c r="J54" s="58"/>
       <c r="L54" t="s">
-        <v>892</v>
+        <v>1655</v>
       </c>
       <c r="AU54" s="103" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -51881,10 +51878,10 @@
         <v>703</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -52384,7 +52381,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="134.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -52403,10 +52400,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>417</v>
@@ -52456,7 +52453,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="131" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -52506,7 +52503,7 @@
         <v>626</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -52518,7 +52515,7 @@
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
@@ -52529,16 +52526,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>394</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
@@ -52550,7 +52547,7 @@
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -52562,7 +52559,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -52582,7 +52579,7 @@
         <v>559</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -52594,7 +52591,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -52606,7 +52603,7 @@
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="E10" s="32" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -52618,7 +52615,7 @@
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="E11" s="32" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -52630,7 +52627,7 @@
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -52642,7 +52639,7 @@
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -52654,7 +52651,7 @@
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -52666,7 +52663,7 @@
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -52678,7 +52675,7 @@
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -52690,7 +52687,7 @@
       <c r="C17" s="32"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -52702,7 +52699,7 @@
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -52714,7 +52711,7 @@
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
       <c r="E19" s="32" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -52726,7 +52723,7 @@
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -52738,7 +52735,7 @@
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
@@ -52750,7 +52747,7 @@
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -52762,7 +52759,7 @@
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
@@ -52774,7 +52771,7 @@
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
@@ -52786,7 +52783,7 @@
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
       <c r="E25" s="32" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -52798,7 +52795,7 @@
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
       <c r="E26" s="32" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -52810,7 +52807,7 @@
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
       <c r="E27" s="32" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
@@ -52822,7 +52819,7 @@
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
       <c r="E28" s="32" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
@@ -52834,7 +52831,7 @@
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="E29" s="32" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="F29" s="32"/>
       <c r="G29" s="32"/>
@@ -52846,7 +52843,7 @@
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="E30" s="32" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="F30" s="32"/>
       <c r="G30" s="32"/>
@@ -52858,7 +52855,7 @@
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="E31" s="32" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="F31" s="32"/>
       <c r="G31" s="32"/>
@@ -52870,7 +52867,7 @@
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="E32" s="32" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="F32" s="32"/>
       <c r="G32" s="32"/>
@@ -52882,7 +52879,7 @@
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="E33" s="32" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -52894,7 +52891,7 @@
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="E34" s="32" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="F34" s="32"/>
       <c r="G34" s="32"/>
@@ -52906,7 +52903,7 @@
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="E35" s="32" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="F35" s="32"/>
       <c r="G35" s="32"/>
@@ -52918,7 +52915,7 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -52930,7 +52927,7 @@
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="32" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
@@ -52942,7 +52939,7 @@
       <c r="C38" s="32"/>
       <c r="D38" s="32"/>
       <c r="E38" s="32" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
@@ -52954,7 +52951,7 @@
       <c r="C39" s="32"/>
       <c r="D39" s="32"/>
       <c r="E39" s="32" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
@@ -52966,7 +52963,7 @@
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
       <c r="E40" s="32" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
@@ -52978,7 +52975,7 @@
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
       <c r="E41" s="32" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="F41" s="32"/>
       <c r="G41" s="32"/>
@@ -52990,7 +52987,7 @@
       <c r="C42" s="32"/>
       <c r="D42" s="32"/>
       <c r="E42" s="32" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
@@ -53002,7 +52999,7 @@
       <c r="C43" s="32"/>
       <c r="D43" s="32"/>
       <c r="E43" s="32" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="F43" s="32"/>
       <c r="G43" s="32"/>
@@ -53014,7 +53011,7 @@
       <c r="C44" s="32"/>
       <c r="D44" s="32"/>
       <c r="E44" s="32" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
@@ -53026,7 +53023,7 @@
       <c r="C45" s="32"/>
       <c r="D45" s="32"/>
       <c r="E45" s="32" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="F45" s="32"/>
       <c r="G45" s="32"/>
@@ -53038,7 +53035,7 @@
       <c r="C46" s="32"/>
       <c r="D46" s="32"/>
       <c r="E46" s="32" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
@@ -53050,7 +53047,7 @@
       <c r="C47" s="32"/>
       <c r="D47" s="32"/>
       <c r="E47" s="32" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="F47" s="32"/>
       <c r="G47" s="32"/>
@@ -53062,7 +53059,7 @@
       <c r="C48" s="32"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
@@ -53074,7 +53071,7 @@
       <c r="C49" s="32"/>
       <c r="D49" s="32"/>
       <c r="E49" s="32" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
@@ -53086,7 +53083,7 @@
       <c r="C50" s="32"/>
       <c r="D50" s="32"/>
       <c r="E50" s="32" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
@@ -53106,7 +53103,7 @@
         <v>561</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
@@ -53118,7 +53115,7 @@
       <c r="C52" s="32"/>
       <c r="D52" s="32"/>
       <c r="E52" s="32" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="F52" s="32"/>
       <c r="G52" s="32"/>
@@ -53130,7 +53127,7 @@
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
       <c r="E53" s="32" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="F53" s="32"/>
       <c r="G53" s="32"/>
@@ -53142,7 +53139,7 @@
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
       <c r="E54" s="32" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
@@ -53154,7 +53151,7 @@
       <c r="C55" s="32"/>
       <c r="D55" s="32"/>
       <c r="E55" s="32" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
@@ -53166,7 +53163,7 @@
       <c r="C56" s="32"/>
       <c r="D56" s="32"/>
       <c r="E56" s="32" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="F56" s="32"/>
       <c r="G56" s="32"/>
@@ -53178,7 +53175,7 @@
       <c r="C57" s="32"/>
       <c r="D57" s="32"/>
       <c r="E57" s="32" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="F57" s="32"/>
       <c r="G57" s="32"/>
@@ -53190,7 +53187,7 @@
       <c r="C58" s="32"/>
       <c r="D58" s="32"/>
       <c r="E58" s="32" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="F58" s="32"/>
       <c r="G58" s="32"/>
@@ -53202,7 +53199,7 @@
       <c r="C59" s="32"/>
       <c r="D59" s="32"/>
       <c r="E59" s="32" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="F59" s="32"/>
       <c r="G59" s="32"/>
@@ -53214,7 +53211,7 @@
       <c r="C60" s="32"/>
       <c r="D60" s="32"/>
       <c r="E60" s="32" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="F60" s="32"/>
       <c r="G60" s="32"/>
@@ -53226,7 +53223,7 @@
       <c r="C61" s="32"/>
       <c r="D61" s="32"/>
       <c r="E61" s="32" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="F61" s="32"/>
       <c r="G61" s="32"/>
@@ -53238,7 +53235,7 @@
       <c r="C62" s="32"/>
       <c r="D62" s="32"/>
       <c r="E62" s="32" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="F62" s="32"/>
       <c r="G62" s="32"/>
@@ -53250,7 +53247,7 @@
       <c r="C63" s="32"/>
       <c r="D63" s="32"/>
       <c r="E63" s="32" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="F63" s="32"/>
       <c r="G63" s="32"/>
@@ -53262,7 +53259,7 @@
       <c r="C64" s="32"/>
       <c r="D64" s="32"/>
       <c r="E64" s="32" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="F64" s="32"/>
       <c r="G64" s="32"/>
@@ -53274,7 +53271,7 @@
       <c r="C65" s="32"/>
       <c r="D65" s="32"/>
       <c r="E65" s="32" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="F65" s="32"/>
       <c r="G65" s="32"/>
@@ -53286,7 +53283,7 @@
       <c r="C66" s="32"/>
       <c r="D66" s="32"/>
       <c r="E66" s="32" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="F66" s="32"/>
       <c r="G66" s="32"/>
@@ -53298,7 +53295,7 @@
       <c r="C67" s="32"/>
       <c r="D67" s="32"/>
       <c r="E67" s="32" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="F67" s="32"/>
       <c r="G67" s="32"/>
@@ -53310,7 +53307,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="32" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32"/>
@@ -53322,7 +53319,7 @@
       <c r="C69" s="32"/>
       <c r="D69" s="32"/>
       <c r="E69" s="32" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
@@ -53334,7 +53331,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="32" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32"/>
@@ -53346,7 +53343,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="32" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
@@ -53358,7 +53355,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="32"/>
       <c r="E72" s="32" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
@@ -53370,7 +53367,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
@@ -53382,7 +53379,7 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="32" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -53394,7 +53391,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="32" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32"/>
@@ -53406,7 +53403,7 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="32" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32"/>
@@ -53418,7 +53415,7 @@
       <c r="C77" s="32"/>
       <c r="D77" s="32"/>
       <c r="E77" s="32" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32"/>
@@ -53429,16 +53426,16 @@
         <v>5</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="C78" s="32" t="s">
         <v>394</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="E78" s="131" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="F78" s="32"/>
       <c r="G78" s="32"/>
@@ -53450,7 +53447,7 @@
       <c r="C79" s="32"/>
       <c r="D79" s="32"/>
       <c r="E79" s="32" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="F79" s="32"/>
       <c r="G79" s="32"/>
@@ -53462,7 +53459,7 @@
       <c r="C80" s="32"/>
       <c r="D80" s="32"/>
       <c r="E80" s="32" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="F80" s="32"/>
       <c r="G80" s="32"/>
@@ -53474,7 +53471,7 @@
       <c r="C81" s="32"/>
       <c r="D81" s="32"/>
       <c r="E81" s="32" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="F81" s="32"/>
       <c r="G81" s="32"/>
@@ -53491,10 +53488,10 @@
         <v>394</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="F82" s="32"/>
       <c r="G82" s="32"/>
@@ -53506,7 +53503,7 @@
       <c r="C83" s="32"/>
       <c r="D83" s="32"/>
       <c r="E83" s="32" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="F83" s="32"/>
       <c r="G83" s="32"/>
@@ -53518,7 +53515,7 @@
       <c r="C84" s="32"/>
       <c r="D84" s="32"/>
       <c r="E84" s="32" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="F84" s="32"/>
       <c r="G84" s="32"/>
@@ -53530,7 +53527,7 @@
       <c r="C85" s="32"/>
       <c r="D85" s="32"/>
       <c r="E85" s="32" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="F85" s="32"/>
       <c r="G85" s="32"/>
@@ -53541,7 +53538,7 @@
         <v>5</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C86" s="32" t="s">
         <v>394</v>
@@ -53550,7 +53547,7 @@
         <v>835</v>
       </c>
       <c r="E86" s="32" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="F86" s="32"/>
       <c r="G86" s="32"/>
@@ -53562,7 +53559,7 @@
       <c r="C87" s="32"/>
       <c r="D87" s="32"/>
       <c r="E87" s="32" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="F87" s="32"/>
       <c r="G87" s="32"/>
@@ -53574,7 +53571,7 @@
       <c r="C88" s="32"/>
       <c r="D88" s="32"/>
       <c r="E88" s="32" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="F88" s="32"/>
       <c r="G88" s="32"/>
@@ -53586,7 +53583,7 @@
       <c r="C89" s="32"/>
       <c r="D89" s="32"/>
       <c r="E89" s="32" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="F89" s="32"/>
       <c r="G89" s="32"/>
@@ -53598,7 +53595,7 @@
       <c r="C90" s="32"/>
       <c r="D90" s="32"/>
       <c r="E90" s="32" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="F90" s="32"/>
       <c r="G90" s="32"/>
@@ -53610,7 +53607,7 @@
       <c r="C91" s="32"/>
       <c r="D91" s="32"/>
       <c r="E91" s="32" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="F91" s="32"/>
       <c r="G91" s="32"/>
@@ -53622,7 +53619,7 @@
       <c r="C92" s="32"/>
       <c r="D92" s="32"/>
       <c r="E92" s="32" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="F92" s="32"/>
       <c r="G92" s="32"/>
@@ -53634,7 +53631,7 @@
       <c r="C93" s="32"/>
       <c r="D93" s="32"/>
       <c r="E93" s="32" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="F93" s="32"/>
       <c r="G93" s="32"/>
@@ -53646,7 +53643,7 @@
       <c r="C94" s="32"/>
       <c r="D94" s="32"/>
       <c r="E94" s="32" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="F94" s="104"/>
       <c r="G94" s="32"/>
@@ -53666,7 +53663,7 @@
         <v>836</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="F95" s="32"/>
       <c r="G95" s="32"/>
@@ -53678,7 +53675,7 @@
       <c r="C96" s="32"/>
       <c r="D96" s="32"/>
       <c r="E96" s="32" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="F96" s="32"/>
       <c r="G96" s="32"/>
@@ -53690,7 +53687,7 @@
       <c r="C97" s="32"/>
       <c r="D97" s="32"/>
       <c r="E97" s="32" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="F97" s="32"/>
       <c r="G97" s="32"/>
@@ -53702,7 +53699,7 @@
       <c r="C98" s="32"/>
       <c r="D98" s="32"/>
       <c r="E98" s="29" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="F98" s="32"/>
       <c r="G98" s="32"/>
@@ -53714,7 +53711,7 @@
       <c r="C99" s="32"/>
       <c r="D99" s="32"/>
       <c r="E99" s="29" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="F99" s="32"/>
       <c r="G99" s="32"/>
@@ -53726,7 +53723,7 @@
       <c r="C100" s="32"/>
       <c r="D100" s="32"/>
       <c r="E100" s="29" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="F100" s="32"/>
       <c r="G100" s="32"/>
@@ -53738,7 +53735,7 @@
       <c r="C101" s="32"/>
       <c r="D101" s="32"/>
       <c r="E101" s="29" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="F101" s="32"/>
       <c r="G101" s="32"/>
@@ -53750,7 +53747,7 @@
       <c r="C102" s="32"/>
       <c r="D102" s="32"/>
       <c r="E102" s="29" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="F102" s="32"/>
       <c r="G102" s="32"/>
@@ -53762,7 +53759,7 @@
       <c r="C103" s="32"/>
       <c r="D103" s="32"/>
       <c r="E103" s="29" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="F103" s="32"/>
       <c r="G103" s="32"/>
@@ -53774,7 +53771,7 @@
       <c r="C104" s="32"/>
       <c r="D104" s="32"/>
       <c r="E104" s="29" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="F104" s="32"/>
       <c r="G104" s="32"/>
@@ -53786,7 +53783,7 @@
       <c r="C105" s="32"/>
       <c r="D105" s="32"/>
       <c r="E105" s="29" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="F105" s="32"/>
       <c r="G105" s="32"/>
@@ -53798,7 +53795,7 @@
       <c r="C106" s="32"/>
       <c r="D106" s="32"/>
       <c r="E106" s="29" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F106" s="32"/>
       <c r="G106" s="32"/>
@@ -53810,7 +53807,7 @@
       <c r="C107" s="32"/>
       <c r="D107" s="32"/>
       <c r="E107" s="29" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="F107" s="32"/>
       <c r="G107" s="32"/>
@@ -53822,7 +53819,7 @@
       <c r="C108" s="32"/>
       <c r="D108" s="32"/>
       <c r="E108" s="29" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="F108" s="32"/>
       <c r="G108" s="32"/>
@@ -53834,7 +53831,7 @@
       <c r="C109" s="32"/>
       <c r="D109" s="32"/>
       <c r="E109" s="29" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="F109" s="32"/>
       <c r="G109" s="32"/>
@@ -53846,7 +53843,7 @@
       <c r="C110" s="32"/>
       <c r="D110" s="32"/>
       <c r="E110" s="29" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="F110" s="32"/>
       <c r="G110" s="32"/>
@@ -53858,7 +53855,7 @@
       <c r="C111" s="32"/>
       <c r="D111" s="32"/>
       <c r="E111" s="29" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="F111" s="32"/>
       <c r="G111" s="32"/>
@@ -53870,7 +53867,7 @@
       <c r="C112" s="32"/>
       <c r="D112" s="32"/>
       <c r="E112" s="29" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="F112" s="32"/>
       <c r="G112" s="32"/>
@@ -53882,7 +53879,7 @@
       <c r="C113" s="32"/>
       <c r="D113" s="32"/>
       <c r="E113" s="29" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="F113" s="32"/>
       <c r="G113" s="32"/>
@@ -53894,7 +53891,7 @@
       <c r="C114" s="32"/>
       <c r="D114" s="32"/>
       <c r="E114" s="29" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="F114" s="32"/>
       <c r="G114" s="32"/>
@@ -53906,7 +53903,7 @@
       <c r="C115" s="32"/>
       <c r="D115" s="32"/>
       <c r="E115" s="29" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="F115" s="32"/>
       <c r="G115" s="32"/>
@@ -53918,7 +53915,7 @@
       <c r="C116" s="32"/>
       <c r="D116" s="32"/>
       <c r="E116" s="29" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="F116" s="32"/>
       <c r="G116" s="32"/>
@@ -53930,7 +53927,7 @@
       <c r="C117" s="32"/>
       <c r="D117" s="32"/>
       <c r="E117" s="29" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="F117" s="32"/>
       <c r="G117" s="32"/>
@@ -53942,7 +53939,7 @@
       <c r="C118" s="32"/>
       <c r="D118" s="32"/>
       <c r="E118" s="29" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="F118" s="32"/>
       <c r="G118" s="32"/>
@@ -53954,7 +53951,7 @@
       <c r="C119" s="32"/>
       <c r="D119" s="32"/>
       <c r="E119" s="29" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="F119" s="32"/>
       <c r="G119" s="32"/>
@@ -53966,7 +53963,7 @@
       <c r="C120" s="32"/>
       <c r="D120" s="32"/>
       <c r="E120" s="29" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="F120" s="32"/>
       <c r="G120" s="32"/>
@@ -53978,7 +53975,7 @@
       <c r="C121" s="32"/>
       <c r="D121" s="32"/>
       <c r="E121" s="29" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="F121" s="32"/>
       <c r="G121" s="32"/>
@@ -53990,7 +53987,7 @@
       <c r="C122" s="32"/>
       <c r="D122" s="32"/>
       <c r="E122" s="29" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="F122" s="32"/>
       <c r="G122" s="32"/>
@@ -54002,7 +53999,7 @@
       <c r="C123" s="32"/>
       <c r="D123" s="32"/>
       <c r="E123" s="29" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="F123" s="32"/>
       <c r="G123" s="32"/>
@@ -54014,7 +54011,7 @@
       <c r="C124" s="32"/>
       <c r="D124" s="32"/>
       <c r="E124" s="29" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="F124" s="32"/>
       <c r="G124" s="32"/>
@@ -54026,7 +54023,7 @@
       <c r="C125" s="32"/>
       <c r="D125" s="32"/>
       <c r="E125" s="29" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="F125" s="32"/>
       <c r="G125" s="32"/>
@@ -54038,7 +54035,7 @@
       <c r="C126" s="32"/>
       <c r="D126" s="32"/>
       <c r="E126" s="29" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="F126" s="32"/>
       <c r="G126" s="32"/>
@@ -54050,7 +54047,7 @@
       <c r="C127" s="32"/>
       <c r="D127" s="32"/>
       <c r="E127" s="29" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="F127" s="32"/>
       <c r="G127" s="32"/>
@@ -54062,7 +54059,7 @@
       <c r="C128" s="32"/>
       <c r="D128" s="32"/>
       <c r="E128" s="29" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="F128" s="32"/>
       <c r="G128" s="32"/>
@@ -54074,7 +54071,7 @@
       <c r="C129" s="32"/>
       <c r="D129" s="32"/>
       <c r="E129" s="29" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="F129" s="32"/>
       <c r="G129" s="32"/>
@@ -54086,7 +54083,7 @@
       <c r="C130" s="32"/>
       <c r="D130" s="32"/>
       <c r="E130" s="29" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="F130" s="32"/>
       <c r="G130" s="32"/>
@@ -54098,7 +54095,7 @@
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="F131" s="32"/>
       <c r="G131" s="32"/>
@@ -54110,7 +54107,7 @@
       <c r="C132" s="32"/>
       <c r="D132" s="32"/>
       <c r="E132" s="32" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="F132" s="32"/>
       <c r="G132" s="32"/>
@@ -54122,7 +54119,7 @@
       <c r="C133" s="32"/>
       <c r="D133" s="32"/>
       <c r="E133" s="32" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="F133" s="32"/>
       <c r="G133" s="32"/>
@@ -54134,7 +54131,7 @@
       <c r="C134" s="32"/>
       <c r="D134" s="32"/>
       <c r="E134" s="32" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="F134" s="32"/>
       <c r="G134" s="32"/>
@@ -54146,7 +54143,7 @@
       <c r="C135" s="32"/>
       <c r="D135" s="32"/>
       <c r="E135" s="32" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="F135" s="32"/>
       <c r="G135" s="32"/>
@@ -54158,7 +54155,7 @@
       <c r="C136" s="32"/>
       <c r="D136" s="32"/>
       <c r="E136" s="32" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="F136" s="32"/>
       <c r="G136" s="32"/>
@@ -54178,7 +54175,7 @@
         <v>564</v>
       </c>
       <c r="E137" s="137" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="F137" s="32"/>
       <c r="G137" s="32"/>
@@ -54190,7 +54187,7 @@
       <c r="C138" s="32"/>
       <c r="D138" s="32"/>
       <c r="E138" s="137" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="F138" s="32"/>
       <c r="G138" s="32"/>
@@ -54202,7 +54199,7 @@
       <c r="C139" s="32"/>
       <c r="D139" s="32"/>
       <c r="E139" s="32" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="F139" s="32"/>
       <c r="G139" s="32"/>
@@ -54214,7 +54211,7 @@
       <c r="C140" s="32"/>
       <c r="D140" s="32"/>
       <c r="E140" s="32" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="F140" s="32"/>
       <c r="G140" s="32"/>
@@ -54226,7 +54223,7 @@
       <c r="C141" s="32"/>
       <c r="D141" s="32"/>
       <c r="E141" s="32" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="F141" s="32"/>
       <c r="G141" s="32"/>
@@ -54238,7 +54235,7 @@
       <c r="C142" s="32"/>
       <c r="D142" s="32"/>
       <c r="E142" s="32" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="F142" s="32"/>
       <c r="G142" s="32"/>
@@ -54250,7 +54247,7 @@
       <c r="C143" s="32"/>
       <c r="D143" s="32"/>
       <c r="E143" s="32" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F143" s="32"/>
       <c r="G143" s="32"/>
@@ -54262,7 +54259,7 @@
       <c r="C144" s="32"/>
       <c r="D144" s="32"/>
       <c r="E144" s="32" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="F144" s="32"/>
       <c r="G144" s="32"/>
@@ -54274,7 +54271,7 @@
       <c r="C145" s="32"/>
       <c r="D145" s="32"/>
       <c r="E145" s="32" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F145" s="32"/>
       <c r="G145" s="32"/>
@@ -54286,7 +54283,7 @@
       <c r="C146" s="32"/>
       <c r="D146" s="32"/>
       <c r="E146" s="32" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="F146" s="32"/>
       <c r="G146" s="32"/>
@@ -54298,7 +54295,7 @@
       <c r="C147" s="32"/>
       <c r="D147" s="32"/>
       <c r="E147" s="32" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="F147" s="32"/>
       <c r="G147" s="32"/>
@@ -54310,7 +54307,7 @@
       <c r="C148" s="32"/>
       <c r="D148" s="32"/>
       <c r="E148" s="32" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F148" s="32"/>
       <c r="G148" s="32"/>
@@ -54322,7 +54319,7 @@
       <c r="C149" s="32"/>
       <c r="D149" s="32"/>
       <c r="E149" s="32" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="F149" s="32"/>
       <c r="G149" s="32"/>
@@ -54334,7 +54331,7 @@
       <c r="C150" s="32"/>
       <c r="D150" s="32"/>
       <c r="E150" s="32" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F150" s="32"/>
       <c r="G150" s="32"/>
@@ -54346,7 +54343,7 @@
       <c r="C151" s="32"/>
       <c r="D151" s="32"/>
       <c r="E151" s="32" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="F151" s="32"/>
       <c r="G151" s="32"/>
@@ -54358,7 +54355,7 @@
       <c r="C152" s="32"/>
       <c r="D152" s="32"/>
       <c r="E152" s="32" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="F152" s="32"/>
       <c r="G152" s="32"/>
@@ -54370,7 +54367,7 @@
       <c r="C153" s="32"/>
       <c r="D153" s="32"/>
       <c r="E153" s="32" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="F153" s="32"/>
       <c r="G153" s="32"/>
@@ -54382,7 +54379,7 @@
       <c r="C154" s="32"/>
       <c r="D154" s="32"/>
       <c r="E154" s="32" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="F154" s="32"/>
       <c r="G154" s="32"/>
@@ -54394,7 +54391,7 @@
       <c r="C155" s="32"/>
       <c r="D155" s="32"/>
       <c r="E155" s="32" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="F155" s="32"/>
       <c r="G155" s="32"/>
@@ -54406,7 +54403,7 @@
       <c r="C156" s="32"/>
       <c r="D156" s="32"/>
       <c r="E156" s="32" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="F156" s="32"/>
       <c r="G156" s="32"/>
@@ -54426,7 +54423,7 @@
         <v>566</v>
       </c>
       <c r="E157" s="32" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="F157" s="32"/>
       <c r="G157" s="32"/>
@@ -54438,7 +54435,7 @@
       <c r="C158" s="32"/>
       <c r="D158" s="32"/>
       <c r="E158" s="32" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="F158" s="32"/>
       <c r="G158" s="32"/>
@@ -54450,7 +54447,7 @@
       <c r="C159" s="32"/>
       <c r="D159" s="32"/>
       <c r="E159" s="32" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="F159" s="32"/>
       <c r="G159" s="32"/>
@@ -54462,7 +54459,7 @@
       <c r="C160" s="32"/>
       <c r="D160" s="32"/>
       <c r="E160" s="32" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="F160" s="32"/>
       <c r="G160" s="32"/>
@@ -54474,7 +54471,7 @@
       <c r="C161" s="32"/>
       <c r="D161" s="32"/>
       <c r="E161" s="32" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="F161" s="32"/>
       <c r="G161" s="32"/>
@@ -54486,7 +54483,7 @@
       <c r="C162" s="32"/>
       <c r="D162" s="32"/>
       <c r="E162" s="32" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="F162" s="32"/>
       <c r="G162" s="32"/>
@@ -54498,7 +54495,7 @@
       <c r="C163" s="32"/>
       <c r="D163" s="32"/>
       <c r="E163" s="32" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="F163" s="32"/>
       <c r="G163" s="32"/>
@@ -54510,7 +54507,7 @@
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
       <c r="E164" s="32" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="F164" s="32"/>
       <c r="G164" s="32"/>
@@ -54522,7 +54519,7 @@
       <c r="C165" s="32"/>
       <c r="D165" s="32"/>
       <c r="E165" s="32" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="F165" s="32"/>
       <c r="G165" s="32"/>
@@ -54534,7 +54531,7 @@
       <c r="C166" s="32"/>
       <c r="D166" s="32"/>
       <c r="E166" s="32" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="F166" s="32"/>
       <c r="G166" s="32"/>
@@ -54546,7 +54543,7 @@
       <c r="C167" s="32"/>
       <c r="D167" s="32"/>
       <c r="E167" s="32" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="F167" s="32"/>
       <c r="G167" s="32"/>
@@ -54558,7 +54555,7 @@
       <c r="C168" s="32"/>
       <c r="D168" s="32"/>
       <c r="E168" s="32" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="F168" s="32"/>
       <c r="G168" s="32"/>
@@ -54570,7 +54567,7 @@
       <c r="C169" s="32"/>
       <c r="D169" s="32"/>
       <c r="E169" s="32" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="F169" s="32"/>
       <c r="G169" s="32"/>
@@ -54582,7 +54579,7 @@
       <c r="C170" s="32"/>
       <c r="D170" s="32"/>
       <c r="E170" s="32" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="F170" s="32"/>
       <c r="G170" s="32"/>
@@ -54594,7 +54591,7 @@
       <c r="C171" s="32"/>
       <c r="D171" s="32"/>
       <c r="E171" s="32" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="F171" s="32"/>
       <c r="G171" s="32"/>
@@ -54606,7 +54603,7 @@
       <c r="C172" s="32"/>
       <c r="D172" s="32"/>
       <c r="E172" s="32" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="F172" s="32"/>
       <c r="G172" s="32"/>
@@ -54618,7 +54615,7 @@
       <c r="C173" s="32"/>
       <c r="D173" s="32"/>
       <c r="E173" s="32" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="F173" s="32"/>
       <c r="G173" s="32"/>
@@ -54630,7 +54627,7 @@
       <c r="C174" s="32"/>
       <c r="D174" s="32"/>
       <c r="E174" s="32" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="F174" s="32"/>
       <c r="G174" s="32"/>
@@ -54642,7 +54639,7 @@
       <c r="C175" s="32"/>
       <c r="D175" s="32"/>
       <c r="E175" s="32" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="F175" s="32"/>
       <c r="G175" s="32"/>
@@ -54654,7 +54651,7 @@
       <c r="C176" s="32"/>
       <c r="D176" s="32"/>
       <c r="E176" s="32" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="F176" s="32"/>
       <c r="G176" s="32"/>
@@ -54666,7 +54663,7 @@
       <c r="C177" s="32"/>
       <c r="D177" s="32"/>
       <c r="E177" s="32" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="F177" s="32"/>
       <c r="G177" s="32"/>
@@ -54678,7 +54675,7 @@
       <c r="C178" s="32"/>
       <c r="D178" s="32"/>
       <c r="E178" s="32" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="F178" s="32"/>
       <c r="G178" s="32"/>
@@ -54690,7 +54687,7 @@
       <c r="C179" s="32"/>
       <c r="D179" s="32"/>
       <c r="E179" s="32" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="F179" s="32"/>
       <c r="G179" s="32"/>
@@ -54702,7 +54699,7 @@
       <c r="C180" s="32"/>
       <c r="D180" s="32"/>
       <c r="E180" s="32" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="F180" s="32"/>
       <c r="G180" s="32"/>
@@ -54714,7 +54711,7 @@
       <c r="C181" s="32"/>
       <c r="D181" s="32"/>
       <c r="E181" s="32" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="F181" s="32"/>
       <c r="G181" s="32"/>
@@ -54726,7 +54723,7 @@
       <c r="C182" s="32"/>
       <c r="D182" s="32"/>
       <c r="E182" s="32" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="F182" s="32"/>
       <c r="G182" s="32"/>
@@ -54738,7 +54735,7 @@
       <c r="C183" s="32"/>
       <c r="D183" s="32"/>
       <c r="E183" s="32" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="F183" s="32"/>
       <c r="G183" s="32"/>
@@ -54750,7 +54747,7 @@
       <c r="C184" s="32"/>
       <c r="D184" s="32"/>
       <c r="E184" s="32" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="F184" s="32"/>
       <c r="G184" s="32"/>
@@ -54762,7 +54759,7 @@
       <c r="C185" s="32"/>
       <c r="D185" s="32"/>
       <c r="E185" s="32" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="F185" s="32"/>
       <c r="G185" s="32"/>
@@ -54774,7 +54771,7 @@
       <c r="C186" s="32"/>
       <c r="D186" s="32"/>
       <c r="E186" s="32" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="F186" s="32"/>
       <c r="G186" s="32"/>
@@ -54786,7 +54783,7 @@
       <c r="C187" s="32"/>
       <c r="D187" s="32"/>
       <c r="E187" s="32" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="F187" s="32"/>
       <c r="G187" s="32"/>
@@ -54798,7 +54795,7 @@
       <c r="C188" s="32"/>
       <c r="D188" s="32"/>
       <c r="E188" s="32" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="F188" s="32"/>
       <c r="G188" s="32"/>
@@ -54818,7 +54815,7 @@
         <v>737</v>
       </c>
       <c r="E189" s="95" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="F189" s="32"/>
       <c r="G189" s="32"/>
@@ -54842,7 +54839,7 @@
       <c r="C191" s="32"/>
       <c r="D191" s="32"/>
       <c r="E191" s="32" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="F191" s="32"/>
       <c r="G191" s="32"/>
@@ -54854,7 +54851,7 @@
       <c r="C192" s="32"/>
       <c r="D192" s="32"/>
       <c r="E192" s="32" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="F192" s="32"/>
       <c r="G192" s="32"/>
@@ -54874,7 +54871,7 @@
         <v>568</v>
       </c>
       <c r="E193" s="32" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="F193" s="32"/>
       <c r="G193" s="32"/>
@@ -54886,7 +54883,7 @@
       <c r="C194" s="32"/>
       <c r="D194" s="32"/>
       <c r="E194" s="32" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="F194" s="32"/>
       <c r="G194" s="32"/>
@@ -54898,7 +54895,7 @@
       <c r="C195" s="32"/>
       <c r="D195" s="32"/>
       <c r="E195" s="32" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="F195" s="32"/>
       <c r="G195" s="32"/>
@@ -54910,7 +54907,7 @@
       <c r="C196" s="32"/>
       <c r="D196" s="32"/>
       <c r="E196" s="32" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="F196" s="32"/>
       <c r="G196" s="32"/>
@@ -54922,7 +54919,7 @@
       <c r="C197" s="32"/>
       <c r="D197" s="32"/>
       <c r="E197" s="32" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="F197" s="32"/>
       <c r="G197" s="32"/>
@@ -54934,7 +54931,7 @@
       <c r="C198" s="32"/>
       <c r="D198" s="32"/>
       <c r="E198" s="32" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="F198" s="32"/>
       <c r="G198" s="32"/>
@@ -54946,7 +54943,7 @@
       <c r="C199" s="32"/>
       <c r="D199" s="32"/>
       <c r="E199" s="32" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="F199" s="32"/>
       <c r="G199" s="32"/>
@@ -54958,7 +54955,7 @@
       <c r="C200" s="32"/>
       <c r="D200" s="32"/>
       <c r="E200" s="32" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="F200" s="32"/>
       <c r="G200" s="32"/>
@@ -54970,7 +54967,7 @@
       <c r="C201" s="32"/>
       <c r="D201" s="32"/>
       <c r="E201" s="32" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="F201" s="32"/>
       <c r="G201" s="32"/>
@@ -54982,7 +54979,7 @@
       <c r="C202" s="32"/>
       <c r="D202" s="32"/>
       <c r="E202" s="32" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="F202" s="32"/>
       <c r="G202" s="32"/>
@@ -54994,7 +54991,7 @@
       <c r="C203" s="32"/>
       <c r="D203" s="32"/>
       <c r="E203" s="32" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="F203" s="32"/>
       <c r="G203" s="32"/>
@@ -55006,7 +55003,7 @@
       <c r="C204" s="32"/>
       <c r="D204" s="32"/>
       <c r="E204" s="32" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="F204" s="32"/>
       <c r="G204" s="32"/>
@@ -55018,7 +55015,7 @@
       <c r="C205" s="32"/>
       <c r="D205" s="32"/>
       <c r="E205" s="32" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="F205" s="32"/>
       <c r="G205" s="32"/>
@@ -55030,7 +55027,7 @@
       <c r="C206" s="32"/>
       <c r="D206" s="32"/>
       <c r="E206" s="32" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="F206" s="32"/>
       <c r="G206" s="32"/>
@@ -55042,7 +55039,7 @@
       <c r="C207" s="32"/>
       <c r="D207" s="32"/>
       <c r="E207" s="32" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="F207" s="32"/>
       <c r="G207" s="32"/>
@@ -55054,7 +55051,7 @@
       <c r="C208" s="32"/>
       <c r="D208" s="32"/>
       <c r="E208" s="32" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="F208" s="32"/>
       <c r="G208" s="32"/>
@@ -55066,7 +55063,7 @@
       <c r="C209" s="32"/>
       <c r="D209" s="32"/>
       <c r="E209" s="32" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="F209" s="32"/>
       <c r="G209" s="32"/>
@@ -55078,7 +55075,7 @@
       <c r="C210" s="32"/>
       <c r="D210" s="32"/>
       <c r="E210" s="32" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="F210" s="32"/>
       <c r="G210" s="32"/>
@@ -55090,7 +55087,7 @@
       <c r="C211" s="32"/>
       <c r="D211" s="32"/>
       <c r="E211" s="32" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="F211" s="32"/>
       <c r="G211" s="32"/>
@@ -55102,7 +55099,7 @@
       <c r="C212" s="32"/>
       <c r="D212" s="32"/>
       <c r="E212" s="32" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="F212" s="32"/>
       <c r="G212" s="32"/>
@@ -55114,7 +55111,7 @@
       <c r="C213" s="32"/>
       <c r="D213" s="32"/>
       <c r="E213" s="32" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="F213" s="32"/>
       <c r="G213" s="32"/>
@@ -55126,7 +55123,7 @@
       <c r="C214" s="32"/>
       <c r="D214" s="32"/>
       <c r="E214" s="32" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="F214" s="32"/>
       <c r="G214" s="32"/>
@@ -55138,7 +55135,7 @@
       <c r="C215" s="32"/>
       <c r="D215" s="32"/>
       <c r="E215" s="32" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="F215" s="32"/>
       <c r="G215" s="32"/>
@@ -55150,7 +55147,7 @@
       <c r="C216" s="32"/>
       <c r="D216" s="32"/>
       <c r="E216" s="32" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="F216" s="32"/>
       <c r="G216" s="32"/>
@@ -55162,7 +55159,7 @@
       <c r="C217" s="32"/>
       <c r="D217" s="32"/>
       <c r="E217" s="32" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="F217" s="32"/>
       <c r="G217" s="32"/>
@@ -55174,7 +55171,7 @@
       <c r="C218" s="32"/>
       <c r="D218" s="32"/>
       <c r="E218" s="32" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="F218" s="32"/>
       <c r="G218" s="32"/>
@@ -55186,7 +55183,7 @@
       <c r="C219" s="32"/>
       <c r="D219" s="32"/>
       <c r="E219" s="32" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="F219" s="32"/>
       <c r="G219" s="32"/>
@@ -55198,7 +55195,7 @@
       <c r="C220" s="32"/>
       <c r="D220" s="32"/>
       <c r="E220" s="32" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F220" s="32"/>
       <c r="G220" s="32"/>
@@ -55210,7 +55207,7 @@
       <c r="C221" s="32"/>
       <c r="D221" s="32"/>
       <c r="E221" s="32" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="F221" s="32"/>
       <c r="G221" s="32"/>
@@ -55222,7 +55219,7 @@
       <c r="C222" s="32"/>
       <c r="D222" s="32"/>
       <c r="E222" s="32" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="F222" s="32"/>
       <c r="G222" s="32"/>
@@ -55234,7 +55231,7 @@
       <c r="C223" s="32"/>
       <c r="D223" s="32"/>
       <c r="E223" s="32" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="F223" s="32"/>
       <c r="G223" s="32"/>
@@ -55246,7 +55243,7 @@
       <c r="C224" s="32"/>
       <c r="D224" s="32"/>
       <c r="E224" s="32" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="F224" s="32"/>
       <c r="G224" s="32"/>
@@ -55258,7 +55255,7 @@
       <c r="C225" s="32"/>
       <c r="D225" s="32"/>
       <c r="E225" s="32" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="F225" s="32"/>
       <c r="G225" s="32"/>
@@ -55270,7 +55267,7 @@
       <c r="C226" s="32"/>
       <c r="D226" s="32"/>
       <c r="E226" s="32" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="F226" s="32"/>
       <c r="G226" s="32"/>
@@ -55282,7 +55279,7 @@
       <c r="C227" s="32"/>
       <c r="D227" s="32"/>
       <c r="E227" s="32" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="F227" s="32"/>
       <c r="G227" s="32"/>
@@ -55294,7 +55291,7 @@
       <c r="C228" s="32"/>
       <c r="D228" s="32"/>
       <c r="E228" s="32" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="F228" s="32"/>
       <c r="G228" s="32"/>
@@ -55306,7 +55303,7 @@
       <c r="C229" s="32"/>
       <c r="D229" s="32"/>
       <c r="E229" s="32" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="F229" s="32"/>
       <c r="G229" s="32"/>
@@ -55318,7 +55315,7 @@
       <c r="C230" s="32"/>
       <c r="D230" s="32"/>
       <c r="E230" s="32" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="F230" s="32"/>
       <c r="G230" s="32"/>
@@ -55330,7 +55327,7 @@
       <c r="C231" s="32"/>
       <c r="D231" s="32"/>
       <c r="E231" s="32" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
       <c r="F231" s="32"/>
       <c r="G231" s="32"/>
@@ -55342,7 +55339,7 @@
       <c r="C232" s="32"/>
       <c r="D232" s="32"/>
       <c r="E232" s="32" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="F232" s="32"/>
       <c r="G232" s="32"/>
@@ -55354,7 +55351,7 @@
       <c r="C233" s="32"/>
       <c r="D233" s="32"/>
       <c r="E233" s="32" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="F233" s="32"/>
       <c r="G233" s="32"/>
@@ -55366,7 +55363,7 @@
       <c r="C234" s="32"/>
       <c r="D234" s="32"/>
       <c r="E234" s="32" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="F234" s="32"/>
       <c r="G234" s="32"/>
@@ -55378,7 +55375,7 @@
       <c r="C235" s="32"/>
       <c r="D235" s="32"/>
       <c r="E235" s="32" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="F235" s="32"/>
       <c r="G235" s="32"/>
@@ -55390,7 +55387,7 @@
       <c r="C236" s="32"/>
       <c r="D236" s="32"/>
       <c r="E236" s="32" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="F236" s="32"/>
       <c r="G236" s="32"/>
@@ -55402,7 +55399,7 @@
       <c r="C237" s="32"/>
       <c r="D237" s="32"/>
       <c r="E237" s="32" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="F237" s="32"/>
       <c r="G237" s="32"/>
@@ -55414,7 +55411,7 @@
       <c r="C238" s="32"/>
       <c r="D238" s="32"/>
       <c r="E238" s="32" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F238" s="32"/>
       <c r="G238" s="32"/>
@@ -55426,7 +55423,7 @@
       <c r="C239" s="32"/>
       <c r="D239" s="32"/>
       <c r="E239" s="32" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="F239" s="32"/>
       <c r="G239" s="32"/>
@@ -55438,7 +55435,7 @@
       <c r="C240" s="32"/>
       <c r="D240" s="32"/>
       <c r="E240" s="32" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F240" s="32"/>
       <c r="G240" s="32"/>
@@ -55446,7 +55443,7 @@
     </row>
     <row r="241" spans="1:9" s="33" customFormat="1" ht="16">
       <c r="E241" s="32" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="I241" s="134"/>
     </row>
@@ -55456,7 +55453,7 @@
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
       <c r="E242" s="32" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="F242" s="33"/>
       <c r="G242" s="33"/>
@@ -55468,7 +55465,7 @@
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
       <c r="E243" s="32" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="F243" s="33"/>
       <c r="G243" s="33"/>
@@ -55480,7 +55477,7 @@
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
       <c r="E244" s="32" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="F244" s="33"/>
       <c r="G244" s="33"/>
@@ -55500,7 +55497,7 @@
         <v>839</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F245" s="33"/>
       <c r="G245" s="33"/>
@@ -55512,7 +55509,7 @@
       <c r="C246" s="33"/>
       <c r="D246" s="33"/>
       <c r="E246" s="32" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F246" s="33"/>
       <c r="G246" s="33"/>
@@ -55524,7 +55521,7 @@
       <c r="C247" s="33"/>
       <c r="D247" s="33"/>
       <c r="E247" s="32" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F247" s="33"/>
       <c r="G247" s="33"/>
@@ -55536,7 +55533,7 @@
       <c r="C248" s="33"/>
       <c r="D248" s="33"/>
       <c r="E248" s="32" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="F248" s="33"/>
       <c r="G248" s="33"/>
@@ -55548,7 +55545,7 @@
       <c r="C249" s="33"/>
       <c r="D249" s="33"/>
       <c r="E249" s="32" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F249" s="33"/>
       <c r="G249" s="33"/>
@@ -55560,7 +55557,7 @@
       <c r="C250" s="33"/>
       <c r="D250" s="33"/>
       <c r="E250" s="32" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="F250" s="33"/>
       <c r="G250" s="33"/>
@@ -55572,7 +55569,7 @@
       <c r="C251" s="33"/>
       <c r="D251" s="33"/>
       <c r="E251" s="32" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F251" s="33"/>
       <c r="G251" s="33"/>
@@ -55584,7 +55581,7 @@
       <c r="C252" s="33"/>
       <c r="D252" s="33"/>
       <c r="E252" s="32" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F252" s="33"/>
       <c r="G252" s="33"/>
@@ -55596,7 +55593,7 @@
       <c r="C253" s="33"/>
       <c r="D253" s="33"/>
       <c r="E253" s="32" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="F253" s="33"/>
       <c r="G253" s="33"/>
@@ -55608,7 +55605,7 @@
       <c r="C254" s="33"/>
       <c r="D254" s="33"/>
       <c r="E254" s="32" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="F254" s="33"/>
       <c r="G254" s="33"/>
@@ -55620,7 +55617,7 @@
       <c r="C255" s="33"/>
       <c r="D255" s="33"/>
       <c r="E255" s="32" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="F255" s="33"/>
       <c r="G255" s="33"/>
@@ -55632,7 +55629,7 @@
       <c r="C256" s="33"/>
       <c r="D256" s="33"/>
       <c r="E256" s="32" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F256" s="33"/>
       <c r="G256" s="33"/>
@@ -55644,7 +55641,7 @@
       <c r="C257" s="33"/>
       <c r="D257" s="33"/>
       <c r="E257" s="32" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="F257" s="33"/>
       <c r="G257" s="33"/>
@@ -55656,7 +55653,7 @@
       <c r="C258" s="33"/>
       <c r="D258" s="33"/>
       <c r="E258" s="32" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="F258" s="33"/>
       <c r="G258" s="33"/>
@@ -55668,7 +55665,7 @@
       <c r="C259" s="33"/>
       <c r="D259" s="33"/>
       <c r="E259" s="32" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="F259" s="33"/>
       <c r="G259" s="33"/>
@@ -55680,7 +55677,7 @@
       <c r="C260" s="33"/>
       <c r="D260" s="33"/>
       <c r="E260" s="32" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="F260" s="33"/>
       <c r="G260" s="33"/>
@@ -55692,7 +55689,7 @@
       <c r="C261" s="33"/>
       <c r="D261" s="33"/>
       <c r="E261" s="32" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="F261" s="33"/>
       <c r="G261" s="33"/>
@@ -55704,7 +55701,7 @@
       <c r="C262" s="33"/>
       <c r="D262" s="33"/>
       <c r="E262" s="32" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="F262" s="33"/>
       <c r="G262" s="33"/>
@@ -55716,7 +55713,7 @@
       <c r="C263" s="33"/>
       <c r="D263" s="33"/>
       <c r="E263" s="32" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="F263" s="33"/>
       <c r="G263" s="33"/>
@@ -55728,7 +55725,7 @@
       <c r="C264" s="33"/>
       <c r="D264" s="33"/>
       <c r="E264" s="32" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="F264" s="33"/>
       <c r="G264" s="33"/>
@@ -55740,7 +55737,7 @@
       <c r="C265" s="33"/>
       <c r="D265" s="33"/>
       <c r="E265" s="32" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F265" s="33"/>
       <c r="G265" s="33"/>
@@ -55752,7 +55749,7 @@
       <c r="C266" s="33"/>
       <c r="D266" s="33"/>
       <c r="E266" s="32" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="F266" s="33"/>
       <c r="G266" s="33"/>
@@ -55764,7 +55761,7 @@
       <c r="C267" s="33"/>
       <c r="D267" s="33"/>
       <c r="E267" s="32" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="F267" s="33"/>
       <c r="G267" s="33"/>
@@ -55776,7 +55773,7 @@
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="32" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="F268" s="33"/>
       <c r="G268" s="33"/>
@@ -55788,7 +55785,7 @@
       <c r="C269" s="33"/>
       <c r="D269" s="33"/>
       <c r="E269" s="32" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="F269" s="33"/>
       <c r="G269" s="33"/>
@@ -55800,7 +55797,7 @@
       <c r="C270" s="33"/>
       <c r="D270" s="33"/>
       <c r="E270" s="32" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="F270" s="33"/>
       <c r="G270" s="33"/>
@@ -55812,7 +55809,7 @@
       <c r="C271" s="33"/>
       <c r="D271" s="33"/>
       <c r="E271" s="32" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="F271" s="33"/>
       <c r="G271" s="33"/>
@@ -55824,7 +55821,7 @@
       <c r="C272" s="33"/>
       <c r="D272" s="33"/>
       <c r="E272" s="32" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="F272" s="33"/>
       <c r="G272" s="33"/>
@@ -55835,16 +55832,16 @@
         <v>5</v>
       </c>
       <c r="B273" s="32" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="C273" s="33" t="s">
         <v>394</v>
       </c>
       <c r="D273" s="32" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="E273" s="32" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="F273" s="33"/>
       <c r="G273" s="33"/>
@@ -55856,7 +55853,7 @@
       <c r="C274" s="33"/>
       <c r="D274" s="32"/>
       <c r="E274" s="32" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="F274" s="33"/>
       <c r="G274" s="33"/>
@@ -55868,7 +55865,7 @@
       <c r="C275" s="33"/>
       <c r="D275" s="32"/>
       <c r="E275" s="32" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="F275" s="33"/>
       <c r="G275" s="33"/>
@@ -55880,7 +55877,7 @@
       <c r="C276" s="33"/>
       <c r="D276" s="32"/>
       <c r="E276" s="32" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="F276" s="33"/>
       <c r="G276" s="33"/>
@@ -55912,7 +55909,7 @@
         <v>841</v>
       </c>
       <c r="E278" s="32" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="F278" s="32"/>
       <c r="G278" s="32"/>
@@ -55924,7 +55921,7 @@
       <c r="C279" s="32"/>
       <c r="D279" s="32"/>
       <c r="E279" s="32" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="F279" s="32"/>
       <c r="G279" s="32"/>
@@ -55936,7 +55933,7 @@
       <c r="C280" s="32"/>
       <c r="D280" s="32"/>
       <c r="E280" s="32" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="F280" s="32"/>
       <c r="G280" s="32"/>
@@ -55956,7 +55953,7 @@
         <v>843</v>
       </c>
       <c r="E281" s="32" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="F281" s="32"/>
       <c r="G281" s="32"/>
@@ -55968,7 +55965,7 @@
       <c r="C282" s="32"/>
       <c r="D282" s="32"/>
       <c r="E282" s="32" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="F282" s="32"/>
       <c r="G282" s="32"/>
@@ -55980,7 +55977,7 @@
       <c r="C283" s="32"/>
       <c r="D283" s="32"/>
       <c r="E283" s="32" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="F283" s="32"/>
       <c r="G283" s="32"/>
@@ -56122,7 +56119,7 @@
       <c r="E1" s="145"/>
       <c r="F1" s="146"/>
       <c r="G1" s="147" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="H1" s="148"/>
       <c r="I1" s="149"/>
@@ -56186,7 +56183,7 @@
         <v>296</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="G4" s="53" t="b">
         <v>0</v>
@@ -56215,7 +56212,7 @@
         <v>298</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="G5" s="53" t="b">
         <v>0</v>
@@ -56236,13 +56233,13 @@
         <v>299</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="E6" s="53" t="s">
         <v>300</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -56267,7 +56264,7 @@
         <v>301</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="G7" s="53" t="b">
         <v>0</v>
@@ -56292,7 +56289,7 @@
         <v>302</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="G8" s="53" t="b">
         <v>0</v>
@@ -56311,7 +56308,7 @@
         <v>303</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="E9" s="53" t="s">
         <v>304</v>
@@ -56338,13 +56335,13 @@
         <v>303</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="E10" s="53" t="s">
         <v>306</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="G10" s="53" t="b">
         <v>0</v>
@@ -56363,13 +56360,13 @@
         <v>303</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="E11" s="53" t="s">
         <v>307</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="G11" s="53" t="b">
         <v>0</v>
@@ -56388,13 +56385,13 @@
         <v>303</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="E12" s="53" t="s">
         <v>308</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="G12" s="53" t="b">
         <v>0</v>
@@ -56491,7 +56488,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="92" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -56509,7 +56506,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="E2" s="107" t="s">
         <v>417</v>
@@ -56520,13 +56517,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -56581,7 +56578,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="40" customFormat="1" ht="207" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -56608,34 +56605,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="106" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E2" s="107" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F2" s="107" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G2" s="107" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H2" s="108" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I2" s="109" t="s">
         <v>1086</v>
       </c>
-      <c r="E2" s="107" t="s">
+      <c r="J2" s="109" t="s">
         <v>1087</v>
       </c>
-      <c r="F2" s="107" t="s">
+      <c r="K2" s="107" t="s">
         <v>1088</v>
       </c>
-      <c r="G2" s="107" t="s">
+      <c r="L2" s="107" t="s">
         <v>1089</v>
       </c>
-      <c r="H2" s="108" t="s">
+      <c r="M2" s="107" t="s">
         <v>1090</v>
-      </c>
-      <c r="I2" s="109" t="s">
-        <v>1091</v>
-      </c>
-      <c r="J2" s="109" t="s">
-        <v>1092</v>
-      </c>
-      <c r="K2" s="107" t="s">
-        <v>1093</v>
-      </c>
-      <c r="L2" s="107" t="s">
-        <v>1094</v>
-      </c>
-      <c r="M2" s="107" t="s">
-        <v>1095</v>
       </c>
       <c r="N2" s="110" t="s">
         <v>417</v>
@@ -56646,29 +56643,29 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>394</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="G3" s="32">
         <v>10</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="112" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="J3" s="112" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="K3" s="32"/>
       <c r="L3" s="32"/>
@@ -56680,19 +56677,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="G4" s="32">
         <v>100</v>
@@ -56703,7 +56700,7 @@
       <c r="I4" s="112"/>
       <c r="J4" s="112"/>
       <c r="K4" s="32" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="L4" s="113"/>
       <c r="M4" s="32"/>
@@ -56721,13 +56718,13 @@
       <c r="I5" s="112"/>
       <c r="J5" s="112"/>
       <c r="K5" s="32" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="L5" s="33" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="N5" s="114"/>
     </row>
@@ -56743,10 +56740,10 @@
       <c r="I6" s="112"/>
       <c r="J6" s="112"/>
       <c r="K6" s="32" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="M6" s="32"/>
       <c r="N6" s="114"/>

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C27474C-C124-3D4E-A4EF-387844BB7914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C317F69B-B105-244E-BBF1-8DE00123138F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -803,7 +803,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="1656">
   <si>
     <t>Region</t>
   </si>
@@ -13755,6 +13755,21 @@
     <t>phxcustompolicy</t>
   </si>
   <si>
+    <t>Plugin OS Management Service Agent</t>
+  </si>
+  <si>
+    <t>ashburn</t>
+  </si>
+  <si>
+    <t>chicago</t>
+  </si>
+  <si>
+    <t>london</t>
+  </si>
+  <si>
+    <t>cardiff</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -13796,23 +13811,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Updated Instances sheet, Exa-Infra sheet</t>
-    </r>
-  </si>
-  <si>
-    <t>Plugin OS Management Service Agent</t>
-  </si>
-  <si>
-    <t>ashburn</t>
-  </si>
-  <si>
-    <t>chicago</t>
-  </si>
-  <si>
-    <t>london</t>
-  </si>
-  <si>
-    <t>cardiff</t>
+Updated Instances sheet, Exa-Infra sheet, LB-Listener sheet</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -20123,7 +20123,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="79" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
     </row>
   </sheetData>
@@ -24812,7 +24812,7 @@
         <v>1644</v>
       </c>
       <c r="AC2" s="27" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="AD2" s="27" t="s">
         <v>1645</v>
@@ -27173,21 +27173,22 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="13" max="13" width="10.1640625" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="122.25" customHeight="1">
+    <row r="1" spans="1:18" ht="122.25" customHeight="1">
       <c r="A1" s="140" t="s">
         <v>1025</v>
       </c>
@@ -27207,8 +27208,9 @@
       <c r="O1" s="140"/>
       <c r="P1" s="140"/>
       <c r="Q1" s="140"/>
-    </row>
-    <row r="2" spans="1:17" ht="46.5" customHeight="1">
+      <c r="R1" s="140"/>
+    </row>
+    <row r="2" spans="1:18" ht="46.5" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -27221,47 +27223,50 @@
       <c r="D2" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="27" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="I2" s="27" t="s">
         <v>787</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
         <v>795</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>397</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>396</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>436</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="R2" s="27" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" s="33" t="s">
         <v>4</v>
       </c>
@@ -27281,8 +27286,9 @@
       <c r="O3" s="33"/>
       <c r="P3" s="33"/>
       <c r="Q3" s="33"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="33"/>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="53" t="s">
         <v>5</v>
       </c>
@@ -27295,66 +27301,68 @@
       <c r="D4" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="53"/>
+      <c r="F4" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="G4" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="H4" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="53"/>
       <c r="I4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="53"/>
+      <c r="K4" s="53" t="s">
         <v>362</v>
       </c>
-      <c r="K4" s="53"/>
       <c r="L4" s="53"/>
       <c r="M4" s="53"/>
-      <c r="N4" s="53" t="s">
+      <c r="N4" s="53"/>
+      <c r="O4" s="53" t="s">
         <v>411</v>
       </c>
-      <c r="O4" s="86" t="s">
+      <c r="P4" s="86" t="s">
         <v>412</v>
       </c>
-      <c r="P4" s="53">
+      <c r="Q4" s="53">
         <v>2</v>
       </c>
-      <c r="Q4" s="53" t="b">
+      <c r="R4" s="53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5" s="53"/>
       <c r="B5" s="53"/>
       <c r="C5" s="53" t="s">
         <v>169</v>
       </c>
       <c r="D5" s="53"/>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="53"/>
+      <c r="F5" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="G5" s="53" t="s">
         <v>224</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="H5" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="53"/>
       <c r="I5" s="53"/>
-      <c r="J5" s="53" t="s">
+      <c r="J5" s="53"/>
+      <c r="K5" s="53" t="s">
         <v>421</v>
       </c>
-      <c r="K5" s="53"/>
       <c r="L5" s="53"/>
       <c r="M5" s="53"/>
       <c r="N5" s="53"/>
       <c r="O5" s="53"/>
       <c r="P5" s="53"/>
       <c r="Q5" s="53"/>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="53"/>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="53" t="s">
         <v>5</v>
       </c>
@@ -27367,43 +27375,44 @@
       <c r="D6" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="53"/>
+      <c r="F6" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="G6" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="H6" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="I6" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53" t="s">
+      <c r="J6" s="53"/>
+      <c r="K6" s="53" t="s">
         <v>246</v>
       </c>
-      <c r="K6" s="53" t="s">
+      <c r="L6" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="L6" s="53">
+      <c r="M6" s="53">
         <v>80</v>
       </c>
-      <c r="M6" s="53">
+      <c r="N6" s="53">
         <v>5</v>
       </c>
-      <c r="N6" s="53"/>
       <c r="O6" s="53"/>
       <c r="P6" s="53"/>
       <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="B3:J1048576 L3:Q1048576" xr:uid="{7586BB6D-DE4D-2B44-80AE-D5F8CEC276CB}"/>
-    <dataValidation allowBlank="1" prompt="Select an OCI region" sqref="A1:Q1" xr:uid="{5CD27DB1-6AC2-1F40-848A-0116AE4EAFCD}"/>
+    <dataValidation allowBlank="1" sqref="B3:K1048576 M3:R1048576" xr:uid="{7586BB6D-DE4D-2B44-80AE-D5F8CEC276CB}"/>
+    <dataValidation allowBlank="1" prompt="Select an OCI region" sqref="A1:R1" xr:uid="{5CD27DB1-6AC2-1F40-848A-0116AE4EAFCD}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -27424,7 +27433,7 @@
           <x14:formula1>
             <xm:f>drop_down_rule_set!$AG$2:$AG$3</xm:f>
           </x14:formula1>
-          <xm:sqref>K3:K1048576</xm:sqref>
+          <xm:sqref>L3:L1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{745B86F0-C782-EE4F-A610-AA5A83A9C20C}">
           <x14:formula1>
@@ -49348,7 +49357,7 @@
         <v>47</v>
       </c>
       <c r="L49" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="P49" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"DHCP")))</f>
@@ -49391,7 +49400,7 @@
         <v>48</v>
       </c>
       <c r="L50" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="P50" s="59" t="str" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"DHCP")))</f>
@@ -49461,7 +49470,7 @@
       <c r="I53" s="58"/>
       <c r="J53" s="58"/>
       <c r="L53" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="AU53" s="103" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -49480,7 +49489,7 @@
       <c r="I54" s="58"/>
       <c r="J54" s="58"/>
       <c r="L54" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="AU54" s="103" t="str">
         <f t="shared" ca="1" si="1"/>

--- a/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-HubSpoke-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C317F69B-B105-244E-BBF1-8DE00123138F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB639F6E-626B-B740-A7C7-11847E7F3D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19820" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -803,7 +803,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3020" uniqueCount="1661">
   <si>
     <t>Region</t>
   </si>
@@ -13813,6 +13813,21 @@
       <t xml:space="preserve">
 Updated Instances sheet, Exa-Infra sheet, LB-Listener sheet</t>
     </r>
+  </si>
+  <si>
+    <t>Database Server Type</t>
+  </si>
+  <si>
+    <t>Storage Server Type</t>
+  </si>
+  <si>
+    <t>X11M</t>
+  </si>
+  <si>
+    <t>X11M-HC</t>
+  </si>
+  <si>
+    <t>Exadata.X11M</t>
   </si>
 </sst>
 </file>
@@ -14491,7 +14506,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -14908,6 +14923,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -33336,18 +33352,18 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="170" customWidth="1"/>
+    <col min="10" max="10" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="119.25" customHeight="1">
+    <row r="1" spans="1:10" ht="119.25" customHeight="1">
       <c r="A1" s="144" t="s">
         <v>1013</v>
       </c>
@@ -33358,8 +33374,10 @@
       <c r="F1" s="145"/>
       <c r="G1" s="145"/>
       <c r="H1" s="145"/>
-    </row>
-    <row r="2" spans="1:8" ht="48">
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+    </row>
+    <row r="2" spans="1:10" ht="48">
       <c r="A2" s="66" t="s">
         <v>0</v>
       </c>
@@ -33381,23 +33399,29 @@
       <c r="G2" s="66" t="s">
         <v>731</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="H2" s="66" t="s">
+        <v>1656</v>
+      </c>
+      <c r="I2" s="66" t="s">
+        <v>1657</v>
+      </c>
+      <c r="J2" s="69" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="73" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="73"/>
       <c r="C3" s="33"/>
       <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
+      <c r="E3" s="43"/>
       <c r="F3" s="33"/>
       <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="J3" s="33"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="53" t="s">
         <v>313</v>
       </c>
@@ -33411,7 +33435,7 @@
         <v>55</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>907</v>
+        <v>1660</v>
       </c>
       <c r="F4" s="54">
         <v>2</v>
@@ -33419,14 +33443,130 @@
       <c r="G4" s="53">
         <v>3</v>
       </c>
-      <c r="H4" s="54"/>
+      <c r="H4" s="53" t="s">
+        <v>1658</v>
+      </c>
+      <c r="I4" s="53" t="s">
+        <v>1659</v>
+      </c>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="170"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="170"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="170"/>
+      <c r="J6" s="170"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="170"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="170"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="170"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="170"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="170"/>
+      <c r="H8" s="170"/>
+      <c r="I8" s="170"/>
+      <c r="J8" s="170"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="170"/>
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="F9" s="170"/>
+      <c r="G9" s="170"/>
+      <c r="H9" s="170"/>
+      <c r="I9" s="170"/>
+      <c r="J9" s="170"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="170"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="170"/>
+      <c r="H10" s="170"/>
+      <c r="I10" s="170"/>
+      <c r="J10" s="170"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="170"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="170"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="170"/>
+      <c r="I11" s="170"/>
+      <c r="J11" s="170"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="170"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="170"/>
+      <c r="J12" s="170"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="170"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="170"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="170"/>
+      <c r="H13" s="170"/>
+      <c r="I13" s="170"/>
+      <c r="J13" s="170"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="170"/>
+      <c r="C14" s="170"/>
+      <c r="D14" s="170"/>
+      <c r="F14" s="170"/>
+      <c r="G14" s="170"/>
+      <c r="H14" s="170"/>
+      <c r="I14" s="170"/>
+      <c r="J14" s="170"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="170"/>
+      <c r="C15" s="170"/>
+      <c r="D15" s="170"/>
+      <c r="F15" s="170"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="170"/>
+      <c r="I15" s="170"/>
+      <c r="J15" s="170"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="170"/>
+      <c r="C16" s="170"/>
+      <c r="D16" s="170"/>
+      <c r="F16" s="170"/>
+      <c r="G16" s="170"/>
+      <c r="H16" s="170"/>
+      <c r="I16" s="170"/>
+      <c r="J16" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="C3:C1048576 F3:H1048576 A1:H1" xr:uid="{954BEEFC-5C23-5145-884B-DDE7DDB1D60C}"/>
+    <dataValidation allowBlank="1" sqref="F5:XFD1048576 D1:XFD2 C1:C1048576 A1:B2 H4:I4 F3:G4 J3:XFD4" xr:uid="{34FC68B7-4F76-9042-8C69-5C3D83C94490}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -33435,30 +33575,12 @@
   </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{46E68055-D15A-424B-A696-316AF79DDD1C}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BEA055ED-A116-FB4D-9618-87CD17E2FDBD}">
           <x14:formula1>
-            <xm:f>drop_down_rule_set!$W$2:$W$4</xm:f>
+            <xm:f>Database_Dropdown!$E$2:$E$14</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{29E1E721-4184-E942-99B4-20CEC789912D}">
-          <x14:formula1>
-            <xm:f>Database_Dropdown!$E$2:$E$13</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" prompt="Specify Compartment name." xr:uid="{F2E0AD96-E2F4-DC45-A121-78B525A8FD3D}">
-          <x14:formula1>
-            <xm:f>INDIRECT("drop_down_rule_comp!$D$2:$D$"&amp;drop_down_rule_comp!$C$3+1)</xm:f>
-          </x14:formula1>
-          <xm:sqref>B3:B1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{F5C6227C-F9EE-614B-BEC7-8DE2C2F88743}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$55</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
+          <xm:sqref>E4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -44895,7 +45017,9 @@
         <v>752</v>
       </c>
       <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
+      <c r="E14" s="33" t="s">
+        <v>1660</v>
+      </c>
       <c r="F14" s="33"/>
       <c r="H14" s="33" t="s">
         <v>450</v>
